--- a/Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C0ECD3-14F6-4925-87A4-0C91213EC4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991B336D-DCED-4587-B793-855A556161D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -505,7 +505,7 @@
     <numFmt numFmtId="165" formatCode="hh:mm:ss;@"/>
     <numFmt numFmtId="166" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -701,6 +701,12 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -920,7 +926,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1049,6 +1055,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1314,6 +1323,9 @@
                   <c:v>46264</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1402,6 +1414,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>23.666666666666796</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
@@ -1707,6 +1722,9 @@
                   <c:v>46264</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1794,6 +1812,9 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3128,7 +3149,7 @@
         <v>35</v>
       </c>
       <c r="E3" s="6">
-        <f>IF(AND($B3&lt;&gt;"", $G3&lt;&gt;"TBD"), ($B3-$G3)*1440, "")</f>
+        <f t="shared" ref="E3:E66" si="0">IF(AND($B3&lt;&gt;"", $G3&lt;&gt;"TBD"), ($B3-$G3)*1440, "")</f>
         <v>2.9999999999999893</v>
       </c>
       <c r="F3" s="2">
@@ -3154,11 +3175,11 @@
         <v>44</v>
       </c>
       <c r="E4" s="6">
-        <f>IF(AND($B4&lt;&gt;"", $G4&lt;&gt;"TBD"), ($B4-$G4)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>8.999999999999968</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F60" si="0">IF(AND($D4&lt;&gt;"",$C4&lt;&gt;""), $D4-$C4, "")</f>
+        <f t="shared" ref="F4:F60" si="1">IF(AND($D4&lt;&gt;"",$C4&lt;&gt;""), $D4-$C4, "")</f>
         <v>3</v>
       </c>
       <c r="G4" s="9">
@@ -3180,11 +3201,11 @@
         <v>52</v>
       </c>
       <c r="E5" s="6">
-        <f>IF(AND($B5&lt;&gt;"", $G5&lt;&gt;"TBD"), ($B5-$G5)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>19.000000000000092</v>
       </c>
       <c r="F5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G5" s="9">
@@ -3206,11 +3227,11 @@
         <v>55</v>
       </c>
       <c r="E6" s="6">
-        <f>IF(AND($B6&lt;&gt;"", $G6&lt;&gt;"TBD"), ($B6-$G6)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>25.000000000000071</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G6" s="9">
@@ -3232,11 +3253,11 @@
         <v>58</v>
       </c>
       <c r="E7" s="6">
-        <f>IF(AND($B7&lt;&gt;"", $G7&lt;&gt;"TBD"), ($B7-$G7)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>40.000000000000014</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G7" s="9">
@@ -3258,11 +3279,11 @@
         <v>61</v>
       </c>
       <c r="E8" s="6">
-        <f>IF(AND($B8&lt;&gt;"", $G8&lt;&gt;"TBD"), ($B8-$G8)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>63.000000000000099</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G8" s="9">
@@ -3284,11 +3305,11 @@
         <v>33</v>
       </c>
       <c r="E9" s="6">
-        <f>IF(AND($B9&lt;&gt;"", $G9&lt;&gt;"TBD"), ($B9-$G9)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>3.0000000000001492</v>
       </c>
       <c r="F9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G9" s="9">
@@ -3310,11 +3331,11 @@
         <v>44</v>
       </c>
       <c r="E10" s="6">
-        <f>IF(AND($B10&lt;&gt;"", $G10&lt;&gt;"TBD"), ($B10-$G10)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>10.000000000000124</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G10" s="9">
@@ -3336,11 +3357,11 @@
         <v>49</v>
       </c>
       <c r="E11" s="6">
-        <f>IF(AND($B11&lt;&gt;"", $G11&lt;&gt;"TBD"), ($B11-$G11)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>16.000000000000185</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G11" s="9">
@@ -3362,11 +3383,11 @@
         <v>54</v>
       </c>
       <c r="E12" s="6">
-        <f>IF(AND($B12&lt;&gt;"", $G12&lt;&gt;"TBD"), ($B12-$G12)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>24.000000000000234</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G12" s="9">
@@ -3388,11 +3409,11 @@
         <v>60</v>
       </c>
       <c r="E13" s="6">
-        <f>IF(AND($B13&lt;&gt;"", $G13&lt;&gt;"TBD"), ($B13-$G13)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>43.000000000000171</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G13" s="9">
@@ -3414,11 +3435,11 @@
         <v>32</v>
       </c>
       <c r="E14" s="6">
-        <f>IF(AND($B14&lt;&gt;"", $G14&lt;&gt;"TBD"), ($B14-$G14)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>3.0000000000000693</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G14" s="9">
@@ -3440,11 +3461,11 @@
         <v>49</v>
       </c>
       <c r="E15" s="6">
-        <f>IF(AND($B15&lt;&gt;"", $G15&lt;&gt;"TBD"), ($B15-$G15)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>15.000000000000027</v>
       </c>
       <c r="F15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G15" s="9">
@@ -3466,11 +3487,11 @@
         <v>54</v>
       </c>
       <c r="E16" s="6">
-        <f>IF(AND($B16&lt;&gt;"", $G16&lt;&gt;"TBD"), ($B16-$G16)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>26.000000000000068</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G16" s="9">
@@ -3492,11 +3513,11 @@
         <v>58</v>
       </c>
       <c r="E17" s="6">
-        <f>IF(AND($B17&lt;&gt;"", $G17&lt;&gt;"TBD"), ($B17-$G17)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>34.000000000000121</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G17" s="9">
@@ -3518,11 +3539,11 @@
         <v>61</v>
       </c>
       <c r="E18" s="6">
-        <f>IF(AND($B18&lt;&gt;"", $G18&lt;&gt;"TBD"), ($B18-$G18)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="F18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G18" s="9">
@@ -3544,11 +3565,11 @@
         <v>33</v>
       </c>
       <c r="E19" s="6">
-        <f>IF(AND($B19&lt;&gt;"", $G19&lt;&gt;"TBD"), ($B19-$G19)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G19" s="9">
@@ -3570,11 +3591,11 @@
         <v>42</v>
       </c>
       <c r="E20" s="6">
-        <f>IF(AND($B20&lt;&gt;"", $G20&lt;&gt;"TBD"), ($B20-$G20)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>5.9999999999999787</v>
       </c>
       <c r="F20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G20" s="9">
@@ -3596,11 +3617,11 @@
         <v>48</v>
       </c>
       <c r="E21" s="6">
-        <f>IF(AND($B21&lt;&gt;"", $G21&lt;&gt;"TBD"), ($B21-$G21)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999645</v>
       </c>
       <c r="F21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G21" s="9">
@@ -3622,11 +3643,11 @@
         <v>52</v>
       </c>
       <c r="E22" s="6">
-        <f>IF(AND($B22&lt;&gt;"", $G22&lt;&gt;"TBD"), ($B22-$G22)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>15.999999999999943</v>
       </c>
       <c r="F22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G22" s="9">
@@ -3648,11 +3669,11 @@
         <v>55</v>
       </c>
       <c r="E23" s="6">
-        <f>IF(AND($B23&lt;&gt;"", $G23&lt;&gt;"TBD"), ($B23-$G23)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>20.999999999999925</v>
       </c>
       <c r="F23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G23" s="9">
@@ -3674,11 +3695,11 @@
         <v>33</v>
       </c>
       <c r="E24" s="6">
-        <f>IF(AND($B24&lt;&gt;"", $G24&lt;&gt;"TBD"), ($B24-$G24)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F24" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G24" s="9">
@@ -3700,11 +3721,11 @@
         <v>41</v>
       </c>
       <c r="E25" s="6">
-        <f>IF(AND($B25&lt;&gt;"", $G25&lt;&gt;"TBD"), ($B25-$G25)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>4.9999999999999822</v>
       </c>
       <c r="F25" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G25" s="9">
@@ -3726,11 +3747,11 @@
         <v>45</v>
       </c>
       <c r="E26" s="6">
-        <f>IF(AND($B26&lt;&gt;"", $G26&lt;&gt;"TBD"), ($B26-$G26)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>10.000000000000044</v>
       </c>
       <c r="F26" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G26" s="9">
@@ -3752,11 +3773,11 @@
         <v>49</v>
       </c>
       <c r="E27" s="6">
-        <f>IF(AND($B27&lt;&gt;"", $G27&lt;&gt;"TBD"), ($B27-$G27)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>14.00000000000003</v>
       </c>
       <c r="F27" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G27" s="9">
@@ -3778,11 +3799,11 @@
         <v>52</v>
       </c>
       <c r="E28" s="6">
-        <f>IF(AND($B28&lt;&gt;"", $G28&lt;&gt;"TBD"), ($B28-$G28)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>18.000000000000014</v>
       </c>
       <c r="F28" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G28" s="9">
@@ -3804,11 +3825,11 @@
         <v>52</v>
       </c>
       <c r="E29" s="6">
-        <f>IF(AND($B29&lt;&gt;"", $G29&lt;&gt;"TBD"), ($B29-$G29)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>19.000000000000014</v>
       </c>
       <c r="F29" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G29" s="9">
@@ -3830,11 +3851,11 @@
         <v>55</v>
       </c>
       <c r="E30" s="6">
-        <f>IF(AND($B30&lt;&gt;"", $G30&lt;&gt;"TBD"), ($B30-$G30)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>23.999999999999993</v>
       </c>
       <c r="F30" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G30" s="9">
@@ -3856,11 +3877,11 @@
         <v>55</v>
       </c>
       <c r="E31" s="6">
-        <f>IF(AND($B31&lt;&gt;"", $G31&lt;&gt;"TBD"), ($B31-$G31)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>26.999999999999986</v>
       </c>
       <c r="F31" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G31" s="9">
@@ -3882,11 +3903,11 @@
         <v>32</v>
       </c>
       <c r="E32" s="6">
-        <f>IF(AND($B32&lt;&gt;"", $G32&lt;&gt;"TBD"), ($B32-$G32)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F32" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G32" s="9">
@@ -3908,11 +3929,11 @@
         <v>41</v>
       </c>
       <c r="E33" s="6">
-        <f>IF(AND($B33&lt;&gt;"", $G33&lt;&gt;"TBD"), ($B33-$G33)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>5.9999999999999787</v>
       </c>
       <c r="F33" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G33" s="9">
@@ -3934,11 +3955,11 @@
         <v>47</v>
       </c>
       <c r="E34" s="6">
-        <f>IF(AND($B34&lt;&gt;"", $G34&lt;&gt;"TBD"), ($B34-$G34)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>11.999999999999957</v>
       </c>
       <c r="F34" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G34" s="9">
@@ -3960,11 +3981,11 @@
         <v>49</v>
       </c>
       <c r="E35" s="6">
-        <f>IF(AND($B35&lt;&gt;"", $G35&lt;&gt;"TBD"), ($B35-$G35)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>13.99999999999995</v>
       </c>
       <c r="F35" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G35" s="9">
@@ -3986,11 +4007,11 @@
         <v>52</v>
       </c>
       <c r="E36" s="6">
-        <f>IF(AND($B36&lt;&gt;"", $G36&lt;&gt;"TBD"), ($B36-$G36)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>20.999999999999925</v>
       </c>
       <c r="F36" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G36" s="9">
@@ -4012,11 +4033,11 @@
         <v>55</v>
       </c>
       <c r="E37" s="6">
-        <f>IF(AND($B37&lt;&gt;"", $G37&lt;&gt;"TBD"), ($B37-$G37)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>25.999999999999986</v>
       </c>
       <c r="F37" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G37" s="9">
@@ -4038,11 +4059,11 @@
         <v>30</v>
       </c>
       <c r="E38" s="6">
-        <f>IF(AND($B38&lt;&gt;"", $G38&lt;&gt;"TBD"), ($B38-$G38)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F38" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G38" s="9">
@@ -4067,11 +4088,11 @@
         <v>35</v>
       </c>
       <c r="E39" s="6">
-        <f>IF(AND($B39&lt;&gt;"", $G39&lt;&gt;"TBD"), ($B39-$G39)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>3.4833333333332916</v>
       </c>
       <c r="F39" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G39" s="9">
@@ -4093,11 +4114,11 @@
         <v>39</v>
       </c>
       <c r="E40" s="6">
-        <f>IF(AND($B40&lt;&gt;"", $G40&lt;&gt;"TBD"), ($B40-$G40)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>5.4999999999999005</v>
       </c>
       <c r="F40" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G40" s="9">
@@ -4119,11 +4140,11 @@
         <v>42</v>
       </c>
       <c r="E41" s="6">
-        <f>IF(AND($B41&lt;&gt;"", $G41&lt;&gt;"TBD"), ($B41-$G41)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>7.5166666666666693</v>
       </c>
       <c r="F41" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G41" s="9">
@@ -4145,11 +4166,11 @@
         <v>45</v>
       </c>
       <c r="E42" s="6">
-        <f>IF(AND($B42&lt;&gt;"", $G42&lt;&gt;"TBD"), ($B42-$G42)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>9.5166666666666622</v>
       </c>
       <c r="F42" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G42" s="9">
@@ -4171,11 +4192,11 @@
         <v>45</v>
       </c>
       <c r="E43" s="6">
-        <f>IF(AND($B43&lt;&gt;"", $G43&lt;&gt;"TBD"), ($B43-$G43)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>11.533333333333271</v>
       </c>
       <c r="F43" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G43" s="9">
@@ -4197,11 +4218,11 @@
         <v>48</v>
       </c>
       <c r="E44" s="6">
-        <f>IF(AND($B44&lt;&gt;"", $G44&lt;&gt;"TBD"), ($B44-$G44)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>13.533333333333264</v>
       </c>
       <c r="F44" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G44" s="9">
@@ -4223,11 +4244,11 @@
         <v>49</v>
       </c>
       <c r="E45" s="6">
-        <f>IF(AND($B45&lt;&gt;"", $G45&lt;&gt;"TBD"), ($B45-$G45)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>15.549999999999873</v>
       </c>
       <c r="F45" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G45" s="9">
@@ -4249,11 +4270,11 @@
         <v>51</v>
       </c>
       <c r="E46" s="6">
-        <f>IF(AND($B46&lt;&gt;"", $G46&lt;&gt;"TBD"), ($B46-$G46)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>17.549999999999866</v>
       </c>
       <c r="F46" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G46" s="9">
@@ -4275,11 +4296,11 @@
         <v>52</v>
       </c>
       <c r="E47" s="6">
-        <f>IF(AND($B47&lt;&gt;"", $G47&lt;&gt;"TBD"), ($B47-$G47)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>19.566666666666634</v>
       </c>
       <c r="F47" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G47" s="9">
@@ -4301,11 +4322,11 @@
         <v>52</v>
       </c>
       <c r="E48" s="6">
-        <f>IF(AND($B48&lt;&gt;"", $G48&lt;&gt;"TBD"), ($B48-$G48)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>21.583333333333243</v>
       </c>
       <c r="F48" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G48" s="9">
@@ -4327,11 +4348,11 @@
         <v>54</v>
       </c>
       <c r="E49" s="6">
-        <f>IF(AND($B49&lt;&gt;"", $G49&lt;&gt;"TBD"), ($B49-$G49)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>23.583333333333236</v>
       </c>
       <c r="F49" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G49" s="9">
@@ -4353,11 +4374,11 @@
         <v>55</v>
       </c>
       <c r="E50" s="6">
-        <f>IF(AND($B50&lt;&gt;"", $G50&lt;&gt;"TBD"), ($B50-$G50)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>25.583333333333229</v>
       </c>
       <c r="F50" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G50" s="9">
@@ -4379,11 +4400,11 @@
         <v>35</v>
       </c>
       <c r="E51" s="6">
-        <f>IF(AND($B51&lt;&gt;"", $G51&lt;&gt;"TBD"), ($B51-$G51)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>3.1166666666667009</v>
       </c>
       <c r="F51" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G51" s="9">
@@ -4405,11 +4426,11 @@
         <v>38</v>
       </c>
       <c r="E52" s="6">
-        <f>IF(AND($B52&lt;&gt;"", $G52&lt;&gt;"TBD"), ($B52-$G52)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>5.1333333333333897</v>
       </c>
       <c r="F52" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G52" s="9">
@@ -4431,11 +4452,11 @@
         <v>41</v>
       </c>
       <c r="E53" s="6">
-        <f>IF(AND($B53&lt;&gt;"", $G53&lt;&gt;"TBD"), ($B53-$G53)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>7.1333333333333826</v>
       </c>
       <c r="F53" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G53" s="9">
@@ -4457,11 +4478,11 @@
         <v>44</v>
       </c>
       <c r="E54" s="6">
-        <f>IF(AND($B54&lt;&gt;"", $G54&lt;&gt;"TBD"), ($B54-$G54)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>9.1499999999999915</v>
       </c>
       <c r="F54" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G54" s="9">
@@ -4483,11 +4504,11 @@
         <v>44</v>
       </c>
       <c r="E55" s="6">
-        <f>IF(AND($B55&lt;&gt;"", $G55&lt;&gt;"TBD"), ($B55-$G55)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>11.16666666666668</v>
       </c>
       <c r="F55" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G55" s="9">
@@ -4509,11 +4530,11 @@
         <v>47</v>
       </c>
       <c r="E56" s="6">
-        <f>IF(AND($B56&lt;&gt;"", $G56&lt;&gt;"TBD"), ($B56-$G56)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>13.166666666666673</v>
       </c>
       <c r="F56" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G56" s="9">
@@ -4535,11 +4556,11 @@
         <v>49</v>
       </c>
       <c r="E57" s="6">
-        <f>IF(AND($B57&lt;&gt;"", $G57&lt;&gt;"TBD"), ($B57-$G57)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>15.183333333333362</v>
       </c>
       <c r="F57" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G57" s="9">
@@ -4561,11 +4582,11 @@
         <v>49</v>
       </c>
       <c r="E58" s="6">
-        <f>IF(AND($B58&lt;&gt;"", $G58&lt;&gt;"TBD"), ($B58-$G58)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>17.200000000000053</v>
       </c>
       <c r="F58" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G58" s="9">
@@ -4587,11 +4608,11 @@
         <v>52</v>
       </c>
       <c r="E59" s="6">
-        <f>IF(AND($B59&lt;&gt;"", $G59&lt;&gt;"TBD"), ($B59-$G59)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>19.216666666666661</v>
       </c>
       <c r="F59" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G59" s="9">
@@ -4613,11 +4634,11 @@
         <v>52</v>
       </c>
       <c r="E60" s="6">
-        <f>IF(AND($B60&lt;&gt;"", $G60&lt;&gt;"TBD"), ($B60-$G60)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>21.216666666666654</v>
       </c>
       <c r="F60" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G60" s="9">
@@ -4639,11 +4660,11 @@
         <v>55</v>
       </c>
       <c r="E61" s="6">
-        <f>IF(AND($B61&lt;&gt;"", $G61&lt;&gt;"TBD"), ($B61-$G61)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>23.216666666666647</v>
       </c>
       <c r="F61" s="2">
-        <f t="shared" ref="F61:F124" si="1">IF(AND($D61&lt;&gt;"",$C61&lt;&gt;""), $D61-$C61, "")</f>
+        <f t="shared" ref="F61:F124" si="2">IF(AND($D61&lt;&gt;"",$C61&lt;&gt;""), $D61-$C61, "")</f>
         <v>3</v>
       </c>
       <c r="G61" s="9">
@@ -4665,11 +4686,11 @@
         <v>55</v>
       </c>
       <c r="E62" s="6">
-        <f>IF(AND($B62&lt;&gt;"", $G62&lt;&gt;"TBD"), ($B62-$G62)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>25.233333333333334</v>
       </c>
       <c r="F62" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G62" s="9">
@@ -4691,11 +4712,11 @@
         <v>55</v>
       </c>
       <c r="E63" s="6">
-        <f>IF(AND($B63&lt;&gt;"", $G63&lt;&gt;"TBD"), ($B63-$G63)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>27.233333333333327</v>
       </c>
       <c r="F63" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G63" s="9">
@@ -4717,11 +4738,11 @@
         <v>31</v>
       </c>
       <c r="E64" s="6">
-        <f>IF(AND($B64&lt;&gt;"", $G64&lt;&gt;"TBD"), ($B64-$G64)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F64" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G64" s="9">
@@ -4743,11 +4764,11 @@
         <v>38</v>
       </c>
       <c r="E65" s="6">
-        <f>IF(AND($B65&lt;&gt;"", $G65&lt;&gt;"TBD"), ($B65-$G65)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>3.9999999999999858</v>
       </c>
       <c r="F65" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G65" s="9">
@@ -4769,11 +4790,11 @@
         <v>44</v>
       </c>
       <c r="E66" s="6">
-        <f>IF(AND($B66&lt;&gt;"", $G66&lt;&gt;"TBD"), ($B66-$G66)*1440, "")</f>
+        <f t="shared" si="0"/>
         <v>8.999999999999968</v>
       </c>
       <c r="F66" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G66" s="9">
@@ -4795,11 +4816,11 @@
         <v>51</v>
       </c>
       <c r="E67" s="6">
-        <f>IF(AND($B67&lt;&gt;"", $G67&lt;&gt;"TBD"), ($B67-$G67)*1440, "")</f>
+        <f t="shared" ref="E67:E130" si="3">IF(AND($B67&lt;&gt;"", $G67&lt;&gt;"TBD"), ($B67-$G67)*1440, "")</f>
         <v>16.99999999999994</v>
       </c>
       <c r="F67" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G67" s="9">
@@ -4821,11 +4842,11 @@
         <v>39</v>
       </c>
       <c r="E68" s="6">
-        <f>IF(AND($B68&lt;&gt;"", $G68&lt;&gt;"TBD"), ($B68-$G68)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>5.0166666666665982</v>
       </c>
       <c r="F68" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G68" s="9">
@@ -4847,11 +4868,11 @@
         <v>45</v>
       </c>
       <c r="E69" s="6">
-        <f>IF(AND($B69&lt;&gt;"", $G69&lt;&gt;"TBD"), ($B69-$G69)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>11.033333333333273</v>
       </c>
       <c r="F69" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G69" s="9">
@@ -4873,11 +4894,11 @@
         <v>48</v>
       </c>
       <c r="E70" s="6">
-        <f>IF(AND($B70&lt;&gt;"", $G70&lt;&gt;"TBD"), ($B70-$G70)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>13.049999999999962</v>
       </c>
       <c r="F70" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G70" s="9">
@@ -4899,11 +4920,11 @@
         <v>49</v>
       </c>
       <c r="E71" s="6">
-        <f>IF(AND($B71&lt;&gt;"", $G71&lt;&gt;"TBD"), ($B71-$G71)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>15.049999999999955</v>
       </c>
       <c r="F71" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G71" s="9">
@@ -4925,11 +4946,11 @@
         <v>52</v>
       </c>
       <c r="E72" s="6">
-        <f>IF(AND($B72&lt;&gt;"", $G72&lt;&gt;"TBD"), ($B72-$G72)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>19.066666666666634</v>
       </c>
       <c r="F72" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G72" s="9">
@@ -4951,11 +4972,11 @@
         <v>52</v>
       </c>
       <c r="E73" s="6">
-        <f>IF(AND($B73&lt;&gt;"", $G73&lt;&gt;"TBD"), ($B73-$G73)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>21.066666666666627</v>
       </c>
       <c r="F73" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G73" s="9">
@@ -4977,11 +4998,11 @@
         <v>55</v>
       </c>
       <c r="E74" s="6">
-        <f>IF(AND($B74&lt;&gt;"", $G74&lt;&gt;"TBD"), ($B74-$G74)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>23.083333333333318</v>
       </c>
       <c r="F74" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G74" s="9">
@@ -5003,11 +5024,11 @@
         <v>55</v>
       </c>
       <c r="E75" s="6">
-        <f>IF(AND($B75&lt;&gt;"", $G75&lt;&gt;"TBD"), ($B75-$G75)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>25.083333333333311</v>
       </c>
       <c r="F75" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G75" s="9">
@@ -5029,11 +5050,11 @@
         <v>55</v>
       </c>
       <c r="E76" s="6">
-        <f>IF(AND($B76&lt;&gt;"", $G76&lt;&gt;"TBD"), ($B76-$G76)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>27.083333333333304</v>
       </c>
       <c r="F76" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G76" s="9">
@@ -5055,11 +5076,11 @@
         <v>55</v>
       </c>
       <c r="E77" s="6">
-        <f>IF(AND($B77&lt;&gt;"", $G77&lt;&gt;"TBD"), ($B77-$G77)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>29.083333333333297</v>
       </c>
       <c r="F77" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G77" s="9">
@@ -5081,11 +5102,11 @@
         <v>58</v>
       </c>
       <c r="E78" s="6">
-        <f>IF(AND($B78&lt;&gt;"", $G78&lt;&gt;"TBD"), ($B78-$G78)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>31.099999999999987</v>
       </c>
       <c r="F78" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G78" s="9">
@@ -5107,11 +5128,11 @@
         <v>31</v>
       </c>
       <c r="E79" s="6">
-        <f>IF(AND($B79&lt;&gt;"", $G79&lt;&gt;"TBD"), ($B79-$G79)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F79" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G79" s="9">
@@ -5133,11 +5154,11 @@
         <v>39</v>
       </c>
       <c r="E80" s="6">
-        <f>IF(AND($B80&lt;&gt;"", $G80&lt;&gt;"TBD"), ($B80-$G80)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>5.5166666666666764</v>
       </c>
       <c r="F80" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G80" s="9">
@@ -5159,11 +5180,11 @@
         <v>42</v>
       </c>
       <c r="E81" s="6">
-        <f>IF(AND($B81&lt;&gt;"", $G81&lt;&gt;"TBD"), ($B81-$G81)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>7.5333333333333652</v>
       </c>
       <c r="F81" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G81" s="9">
@@ -5185,11 +5206,11 @@
         <v>45</v>
       </c>
       <c r="E82" s="6">
-        <f>IF(AND($B82&lt;&gt;"", $G82&lt;&gt;"TBD"), ($B82-$G82)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>9.5333333333333581</v>
       </c>
       <c r="F82" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G82" s="9">
@@ -5211,11 +5232,11 @@
         <v>47</v>
       </c>
       <c r="E83" s="6">
-        <f>IF(AND($B83&lt;&gt;"", $G83&lt;&gt;"TBD"), ($B83-$G83)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>11.549999999999967</v>
       </c>
       <c r="F83" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G83" s="9">
@@ -5237,11 +5258,11 @@
         <v>48</v>
       </c>
       <c r="E84" s="6">
-        <f>IF(AND($B84&lt;&gt;"", $G84&lt;&gt;"TBD"), ($B84-$G84)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>13.566666666666656</v>
       </c>
       <c r="F84" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G84" s="9">
@@ -5263,11 +5284,11 @@
         <v>49</v>
       </c>
       <c r="E85" s="6">
-        <f>IF(AND($B85&lt;&gt;"", $G85&lt;&gt;"TBD"), ($B85-$G85)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>15.583333333333345</v>
       </c>
       <c r="F85" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G85" s="9">
@@ -5289,11 +5310,11 @@
         <v>51</v>
       </c>
       <c r="E86" s="6">
-        <f>IF(AND($B86&lt;&gt;"", $G86&lt;&gt;"TBD"), ($B86-$G86)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>17.583333333333336</v>
       </c>
       <c r="F86" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G86" s="9">
@@ -5315,11 +5336,11 @@
         <v>52</v>
       </c>
       <c r="E87" s="6">
-        <f>IF(AND($B87&lt;&gt;"", $G87&lt;&gt;"TBD"), ($B87-$G87)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>19.600000000000026</v>
       </c>
       <c r="F87" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G87" s="9">
@@ -5341,11 +5362,11 @@
         <v>54</v>
       </c>
       <c r="E88" s="6">
-        <f>IF(AND($B88&lt;&gt;"", $G88&lt;&gt;"TBD"), ($B88-$G88)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>21.600000000000019</v>
       </c>
       <c r="F88" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G88" s="9">
@@ -5367,11 +5388,11 @@
         <v>55</v>
       </c>
       <c r="E89" s="6">
-        <f>IF(AND($B89&lt;&gt;"", $G89&lt;&gt;"TBD"), ($B89-$G89)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>23.600000000000012</v>
       </c>
       <c r="F89" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G89" s="9">
@@ -5393,11 +5414,11 @@
         <v>55</v>
       </c>
       <c r="E90" s="6">
-        <f>IF(AND($B90&lt;&gt;"", $G90&lt;&gt;"TBD"), ($B90-$G90)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>25.599999999999923</v>
       </c>
       <c r="F90" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G90" s="9">
@@ -5419,11 +5440,11 @@
         <v>57</v>
       </c>
       <c r="E91" s="6">
-        <f>IF(AND($B91&lt;&gt;"", $G91&lt;&gt;"TBD"), ($B91-$G91)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>27.616666666666696</v>
       </c>
       <c r="F91" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G91" s="9">
@@ -5445,11 +5466,11 @@
         <v>57</v>
       </c>
       <c r="E92" s="6">
-        <f>IF(AND($B92&lt;&gt;"", $G92&lt;&gt;"TBD"), ($B92-$G92)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>29.633333333333304</v>
       </c>
       <c r="F92" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G92" s="9">
@@ -5471,11 +5492,11 @@
         <v>58</v>
       </c>
       <c r="E93" s="6">
-        <f>IF(AND($B93&lt;&gt;"", $G93&lt;&gt;"TBD"), ($B93-$G93)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>31.633333333333297</v>
       </c>
       <c r="F93" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G93" s="9">
@@ -5497,11 +5518,11 @@
         <v>33</v>
       </c>
       <c r="E94" s="6">
-        <f>IF(AND($B94&lt;&gt;"", $G94&lt;&gt;"TBD"), ($B94-$G94)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F94" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G94" s="9">
@@ -5523,11 +5544,11 @@
         <v>36</v>
       </c>
       <c r="E95" s="6">
-        <f>IF(AND($B95&lt;&gt;"", $G95&lt;&gt;"TBD"), ($B95-$G95)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>4.0499999999999936</v>
       </c>
       <c r="F95" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G95" s="9">
@@ -5549,11 +5570,11 @@
         <v>41</v>
       </c>
       <c r="E96" s="6">
-        <f>IF(AND($B96&lt;&gt;"", $G96&lt;&gt;"TBD"), ($B96-$G96)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>6.0666666666666824</v>
       </c>
       <c r="F96" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G96" s="9">
@@ -5575,11 +5596,11 @@
         <v>44</v>
       </c>
       <c r="E97" s="6">
-        <f>IF(AND($B97&lt;&gt;"", $G97&lt;&gt;"TBD"), ($B97-$G97)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>8.0833333333333712</v>
       </c>
       <c r="F97" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G97" s="9">
@@ -5601,11 +5622,11 @@
         <v>45</v>
       </c>
       <c r="E98" s="6">
-        <f>IF(AND($B98&lt;&gt;"", $G98&lt;&gt;"TBD"), ($B98-$G98)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>10.09999999999998</v>
       </c>
       <c r="F98" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G98" s="9">
@@ -5627,11 +5648,11 @@
         <v>47</v>
       </c>
       <c r="E99" s="6">
-        <f>IF(AND($B99&lt;&gt;"", $G99&lt;&gt;"TBD"), ($B99-$G99)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>12.099999999999973</v>
       </c>
       <c r="F99" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G99" s="9">
@@ -5653,11 +5674,11 @@
         <v>49</v>
       </c>
       <c r="E100" s="6">
-        <f>IF(AND($B100&lt;&gt;"", $G100&lt;&gt;"TBD"), ($B100-$G100)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>14.100000000000046</v>
       </c>
       <c r="F100" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G100" s="9">
@@ -5679,11 +5700,11 @@
         <v>51</v>
       </c>
       <c r="E101" s="6">
-        <f>IF(AND($B101&lt;&gt;"", $G101&lt;&gt;"TBD"), ($B101-$G101)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>16.116666666666653</v>
       </c>
       <c r="F101" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G101" s="9">
@@ -5705,11 +5726,11 @@
         <v>52</v>
       </c>
       <c r="E102" s="6">
-        <f>IF(AND($B102&lt;&gt;"", $G102&lt;&gt;"TBD"), ($B102-$G102)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>18.133333333333344</v>
       </c>
       <c r="F102" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G102" s="9">
@@ -5731,11 +5752,11 @@
         <v>52</v>
       </c>
       <c r="E103" s="6">
-        <f>IF(AND($B103&lt;&gt;"", $G103&lt;&gt;"TBD"), ($B103-$G103)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>20.133333333333336</v>
       </c>
       <c r="F103" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G103" s="9">
@@ -5757,11 +5778,11 @@
         <v>54</v>
       </c>
       <c r="E104" s="6">
-        <f>IF(AND($B104&lt;&gt;"", $G104&lt;&gt;"TBD"), ($B104-$G104)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>22.133333333333329</v>
       </c>
       <c r="F104" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G104" s="9">
@@ -5783,11 +5804,11 @@
         <v>55</v>
       </c>
       <c r="E105" s="6">
-        <f>IF(AND($B105&lt;&gt;"", $G105&lt;&gt;"TBD"), ($B105-$G105)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>24.15000000000002</v>
       </c>
       <c r="F105" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G105" s="9">
@@ -5809,11 +5830,11 @@
         <v>55</v>
       </c>
       <c r="E106" s="6">
-        <f>IF(AND($B106&lt;&gt;"", $G106&lt;&gt;"TBD"), ($B106-$G106)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>26.150000000000013</v>
       </c>
       <c r="F106" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G106" s="9">
@@ -5835,11 +5856,11 @@
         <v>57</v>
       </c>
       <c r="E107" s="6">
-        <f>IF(AND($B107&lt;&gt;"", $G107&lt;&gt;"TBD"), ($B107-$G107)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>28.150000000000006</v>
       </c>
       <c r="F107" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G107" s="9">
@@ -5861,11 +5882,11 @@
         <v>58</v>
       </c>
       <c r="E108" s="6">
-        <f>IF(AND($B108&lt;&gt;"", $G108&lt;&gt;"TBD"), ($B108-$G108)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>30.166666666666693</v>
       </c>
       <c r="F108" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G108" s="9">
@@ -5887,11 +5908,11 @@
         <v>58</v>
       </c>
       <c r="E109" s="6">
-        <f>IF(AND($B109&lt;&gt;"", $G109&lt;&gt;"TBD"), ($B109-$G109)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>32.166666666666686</v>
       </c>
       <c r="F109" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G109" s="9">
@@ -5913,11 +5934,11 @@
         <v>33</v>
       </c>
       <c r="E110" s="6">
-        <f>IF(AND($B110&lt;&gt;"", $G110&lt;&gt;"TBD"), ($B110-$G110)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F110" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G110" s="9">
@@ -5939,11 +5960,11 @@
         <v>35</v>
       </c>
       <c r="E111" s="6">
-        <f>IF(AND($B111&lt;&gt;"", $G111&lt;&gt;"TBD"), ($B111-$G111)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>3.5666666666666913</v>
       </c>
       <c r="F111" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G111" s="9">
@@ -5965,11 +5986,11 @@
         <v>39</v>
       </c>
       <c r="E112" s="6">
-        <f>IF(AND($B112&lt;&gt;"", $G112&lt;&gt;"TBD"), ($B112-$G112)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>5.5666666666666842</v>
       </c>
       <c r="F112" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G112" s="9">
@@ -5991,11 +6012,11 @@
         <v>42</v>
       </c>
       <c r="E113" s="6">
-        <f>IF(AND($B113&lt;&gt;"", $G113&lt;&gt;"TBD"), ($B113-$G113)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>7.5833333333332931</v>
       </c>
       <c r="F113" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G113" s="9">
@@ -6017,11 +6038,11 @@
         <v>45</v>
       </c>
       <c r="E114" s="6">
-        <f>IF(AND($B114&lt;&gt;"", $G114&lt;&gt;"TBD"), ($B114-$G114)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>9.583333333333286</v>
       </c>
       <c r="F114" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G114" s="9">
@@ -6043,11 +6064,11 @@
         <v>47</v>
       </c>
       <c r="E115" s="6">
-        <f>IF(AND($B115&lt;&gt;"", $G115&lt;&gt;"TBD"), ($B115-$G115)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>11.583333333333279</v>
       </c>
       <c r="F115" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G115" s="9">
@@ -6069,11 +6090,11 @@
         <v>49</v>
       </c>
       <c r="E116" s="6">
-        <f>IF(AND($B116&lt;&gt;"", $G116&lt;&gt;"TBD"), ($B116-$G116)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>13.600000000000048</v>
       </c>
       <c r="F116" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="G116" s="9">
@@ -6095,11 +6116,11 @@
         <v>49</v>
       </c>
       <c r="E117" s="6">
-        <f>IF(AND($B117&lt;&gt;"", $G117&lt;&gt;"TBD"), ($B117-$G117)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>15.600000000000041</v>
       </c>
       <c r="F117" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G117" s="9">
@@ -6121,11 +6142,11 @@
         <v>52</v>
       </c>
       <c r="E118" s="6">
-        <f>IF(AND($B118&lt;&gt;"", $G118&lt;&gt;"TBD"), ($B118-$G118)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>17.616666666666649</v>
       </c>
       <c r="F118" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="G118" s="9">
@@ -6147,11 +6168,11 @@
         <v>52</v>
       </c>
       <c r="E119" s="6">
-        <f>IF(AND($B119&lt;&gt;"", $G119&lt;&gt;"TBD"), ($B119-$G119)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>19.616666666666642</v>
       </c>
       <c r="F119" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G119" s="9">
@@ -6173,11 +6194,11 @@
         <v>54</v>
       </c>
       <c r="E120" s="6">
-        <f>IF(AND($B120&lt;&gt;"", $G120&lt;&gt;"TBD"), ($B120-$G120)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>21.616666666666635</v>
       </c>
       <c r="F120" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G120" s="9">
@@ -6199,11 +6220,11 @@
         <v>55</v>
       </c>
       <c r="E121" s="6">
-        <f>IF(AND($B121&lt;&gt;"", $G121&lt;&gt;"TBD"), ($B121-$G121)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>23.616666666666628</v>
       </c>
       <c r="F121" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G121" s="9">
@@ -6225,11 +6246,11 @@
         <v>55</v>
       </c>
       <c r="E122" s="6">
-        <f>IF(AND($B122&lt;&gt;"", $G122&lt;&gt;"TBD"), ($B122-$G122)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>25.633333333333237</v>
       </c>
       <c r="F122" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G122" s="9">
@@ -6251,11 +6272,11 @@
         <v>57</v>
       </c>
       <c r="E123" s="6">
-        <f>IF(AND($B123&lt;&gt;"", $G123&lt;&gt;"TBD"), ($B123-$G123)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>27.63333333333339</v>
       </c>
       <c r="F123" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G123" s="9">
@@ -6277,11 +6298,11 @@
         <v>58</v>
       </c>
       <c r="E124" s="6">
-        <f>IF(AND($B124&lt;&gt;"", $G124&lt;&gt;"TBD"), ($B124-$G124)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>29.65</v>
       </c>
       <c r="F124" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="G124" s="9">
@@ -6303,11 +6324,11 @@
         <v>58</v>
       </c>
       <c r="E125" s="6">
-        <f>IF(AND($B125&lt;&gt;"", $G125&lt;&gt;"TBD"), ($B125-$G125)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>31.649999999999991</v>
       </c>
       <c r="F125" s="2">
-        <f t="shared" ref="F125:F188" si="2">IF(AND($D125&lt;&gt;"",$C125&lt;&gt;""), $D125-$C125, "")</f>
+        <f t="shared" ref="F125:F188" si="4">IF(AND($D125&lt;&gt;"",$C125&lt;&gt;""), $D125-$C125, "")</f>
         <v>3</v>
       </c>
       <c r="G125" s="9">
@@ -6329,11 +6350,11 @@
         <v>30</v>
       </c>
       <c r="E126" s="6">
-        <f>IF(AND($B126&lt;&gt;"", $G126&lt;&gt;"TBD"), ($B126-$G126)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F126" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="G126" s="9">
@@ -6355,11 +6376,11 @@
         <v>33</v>
       </c>
       <c r="E127" s="6">
-        <f>IF(AND($B127&lt;&gt;"", $G127&lt;&gt;"TBD"), ($B127-$G127)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>2.8166666666667339</v>
       </c>
       <c r="F127" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G127" s="9">
@@ -6381,11 +6402,11 @@
         <v>39</v>
       </c>
       <c r="E128" s="6">
-        <f>IF(AND($B128&lt;&gt;"", $G128&lt;&gt;"TBD"), ($B128-$G128)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>4.8166666666667268</v>
       </c>
       <c r="F128" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G128" s="9">
@@ -6407,11 +6428,11 @@
         <v>42</v>
       </c>
       <c r="E129" s="6">
-        <f>IF(AND($B129&lt;&gt;"", $G129&lt;&gt;"TBD"), ($B129-$G129)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>6.8166666666667197</v>
       </c>
       <c r="F129" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G129" s="9">
@@ -6433,11 +6454,11 @@
         <v>45</v>
       </c>
       <c r="E130" s="6">
-        <f>IF(AND($B130&lt;&gt;"", $G130&lt;&gt;"TBD"), ($B130-$G130)*1440, "")</f>
+        <f t="shared" si="3"/>
         <v>8.8333333333333286</v>
       </c>
       <c r="F130" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="G130" s="9">
@@ -6459,11 +6480,11 @@
         <v>45</v>
       </c>
       <c r="E131" s="6">
-        <f>IF(AND($B131&lt;&gt;"", $G131&lt;&gt;"TBD"), ($B131-$G131)*1440, "")</f>
+        <f t="shared" ref="E131:E194" si="5">IF(AND($B131&lt;&gt;"", $G131&lt;&gt;"TBD"), ($B131-$G131)*1440, "")</f>
         <v>10.833333333333401</v>
       </c>
       <c r="F131" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G131" s="9">
@@ -6485,11 +6506,11 @@
         <v>48</v>
       </c>
       <c r="E132" s="6">
-        <f>IF(AND($B132&lt;&gt;"", $G132&lt;&gt;"TBD"), ($B132-$G132)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>12.833333333333394</v>
       </c>
       <c r="F132" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G132" s="9">
@@ -6511,11 +6532,11 @@
         <v>49</v>
       </c>
       <c r="E133" s="6">
-        <f>IF(AND($B133&lt;&gt;"", $G133&lt;&gt;"TBD"), ($B133-$G133)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>14.850000000000003</v>
       </c>
       <c r="F133" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G133" s="9">
@@ -6537,11 +6558,11 @@
         <v>51</v>
       </c>
       <c r="E134" s="6">
-        <f>IF(AND($B134&lt;&gt;"", $G134&lt;&gt;"TBD"), ($B134-$G134)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>16.849999999999994</v>
       </c>
       <c r="F134" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G134" s="9">
@@ -6563,11 +6584,11 @@
         <v>52</v>
       </c>
       <c r="E135" s="6">
-        <f>IF(AND($B135&lt;&gt;"", $G135&lt;&gt;"TBD"), ($B135-$G135)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>18.850000000000069</v>
       </c>
       <c r="F135" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G135" s="9">
@@ -6589,11 +6610,11 @@
         <v>54</v>
       </c>
       <c r="E136" s="6">
-        <f>IF(AND($B136&lt;&gt;"", $G136&lt;&gt;"TBD"), ($B136-$G136)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>20.866666666666678</v>
       </c>
       <c r="F136" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G136" s="9">
@@ -6615,11 +6636,11 @@
         <v>55</v>
       </c>
       <c r="E137" s="6">
-        <f>IF(AND($B137&lt;&gt;"", $G137&lt;&gt;"TBD"), ($B137-$G137)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>22.866666666666671</v>
       </c>
       <c r="F137" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G137" s="9">
@@ -6641,11 +6662,11 @@
         <v>55</v>
       </c>
       <c r="E138" s="6">
-        <f>IF(AND($B138&lt;&gt;"", $G138&lt;&gt;"TBD"), ($B138-$G138)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>24.883333333333361</v>
       </c>
       <c r="F138" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G138" s="9">
@@ -6667,11 +6688,11 @@
         <v>57</v>
       </c>
       <c r="E139" s="6">
-        <f>IF(AND($B139&lt;&gt;"", $G139&lt;&gt;"TBD"), ($B139-$G139)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>26.883333333333354</v>
       </c>
       <c r="F139" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G139" s="9">
@@ -6693,11 +6714,11 @@
         <v>58</v>
       </c>
       <c r="E140" s="6">
-        <f>IF(AND($B140&lt;&gt;"", $G140&lt;&gt;"TBD"), ($B140-$G140)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>28.883333333333347</v>
       </c>
       <c r="F140" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="G140" s="9">
@@ -6719,11 +6740,11 @@
         <v>58</v>
       </c>
       <c r="E141" s="6">
-        <f>IF(AND($B141&lt;&gt;"", $G141&lt;&gt;"TBD"), ($B141-$G141)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>30.900000000000034</v>
       </c>
       <c r="F141" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G141" s="9">
@@ -6745,11 +6766,11 @@
         <v>36</v>
       </c>
       <c r="E142" s="6">
-        <f>IF(AND($B142&lt;&gt;"", $G142&lt;&gt;"TBD"), ($B142-$G142)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>4.0000000000000657</v>
       </c>
       <c r="F142" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G142" s="9">
@@ -6771,11 +6792,11 @@
         <v>38</v>
       </c>
       <c r="E143" s="6">
-        <f>IF(AND($B143&lt;&gt;"", $G143&lt;&gt;"TBD"), ($B143-$G143)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>5.3000000000000291</v>
       </c>
       <c r="F143" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G143" s="9">
@@ -6797,11 +6818,11 @@
         <v>41</v>
       </c>
       <c r="E144" s="6">
-        <f>IF(AND($B144&lt;&gt;"", $G144&lt;&gt;"TBD"), ($B144-$G144)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>7.3166666666667179</v>
       </c>
       <c r="F144" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G144" s="9">
@@ -6823,11 +6844,11 @@
         <v>44</v>
       </c>
       <c r="E145" s="6">
-        <f>IF(AND($B145&lt;&gt;"", $G145&lt;&gt;"TBD"), ($B145-$G145)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>9.3166666666667108</v>
       </c>
       <c r="F145" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G145" s="9">
@@ -6849,11 +6870,11 @@
         <v>45</v>
       </c>
       <c r="E146" s="6">
-        <f>IF(AND($B146&lt;&gt;"", $G146&lt;&gt;"TBD"), ($B146-$G146)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>11.316666666666704</v>
       </c>
       <c r="F146" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G146" s="9">
@@ -6875,11 +6896,11 @@
         <v>47</v>
       </c>
       <c r="E147" s="6">
-        <f>IF(AND($B147&lt;&gt;"", $G147&lt;&gt;"TBD"), ($B147-$G147)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>13.316666666666697</v>
       </c>
       <c r="F147" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G147" s="9">
@@ -6901,11 +6922,11 @@
         <v>49</v>
       </c>
       <c r="E148" s="6">
-        <f>IF(AND($B148&lt;&gt;"", $G148&lt;&gt;"TBD"), ($B148-$G148)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>15.333333333333385</v>
       </c>
       <c r="F148" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="G148" s="9">
@@ -6927,11 +6948,11 @@
         <v>49</v>
       </c>
       <c r="E149" s="6">
-        <f>IF(AND($B149&lt;&gt;"", $G149&lt;&gt;"TBD"), ($B149-$G149)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>17.333333333333378</v>
       </c>
       <c r="F149" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G149" s="9">
@@ -6953,11 +6974,11 @@
         <v>52</v>
       </c>
       <c r="E150" s="6">
-        <f>IF(AND($B150&lt;&gt;"", $G150&lt;&gt;"TBD"), ($B150-$G150)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>19.350000000000065</v>
       </c>
       <c r="F150" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="G150" s="9">
@@ -6979,11 +7000,11 @@
         <v>52</v>
       </c>
       <c r="E151" s="6">
-        <f>IF(AND($B151&lt;&gt;"", $G151&lt;&gt;"TBD"), ($B151-$G151)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>21.350000000000058</v>
       </c>
       <c r="F151" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G151" s="9">
@@ -7005,11 +7026,11 @@
         <v>54</v>
       </c>
       <c r="E152" s="6">
-        <f>IF(AND($B152&lt;&gt;"", $G152&lt;&gt;"TBD"), ($B152-$G152)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>23.350000000000051</v>
       </c>
       <c r="F152" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G152" s="9">
@@ -7031,11 +7052,11 @@
         <v>55</v>
       </c>
       <c r="E153" s="6">
-        <f>IF(AND($B153&lt;&gt;"", $G153&lt;&gt;"TBD"), ($B153-$G153)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>25.366666666666742</v>
       </c>
       <c r="F153" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="G153" s="9">
@@ -7057,11 +7078,11 @@
         <v>55</v>
       </c>
       <c r="E154" s="6">
-        <f>IF(AND($B154&lt;&gt;"", $G154&lt;&gt;"TBD"), ($B154-$G154)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>27.383333333333351</v>
       </c>
       <c r="F154" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G154" s="9">
@@ -7083,11 +7104,11 @@
         <v>57</v>
       </c>
       <c r="E155" s="6">
-        <f>IF(AND($B155&lt;&gt;"", $G155&lt;&gt;"TBD"), ($B155-$G155)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>29.383333333333344</v>
       </c>
       <c r="F155" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G155" s="9">
@@ -7109,11 +7130,11 @@
         <v>57</v>
       </c>
       <c r="E156" s="6">
-        <f>IF(AND($B156&lt;&gt;"", $G156&lt;&gt;"TBD"), ($B156-$G156)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>31.400000000000034</v>
       </c>
       <c r="F156" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G156" s="9">
@@ -7135,11 +7156,11 @@
         <v>58</v>
       </c>
       <c r="E157" s="6">
-        <f>IF(AND($B157&lt;&gt;"", $G157&lt;&gt;"TBD"), ($B157-$G157)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>33.400000000000027</v>
       </c>
       <c r="F157" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="G157" s="9">
@@ -7161,11 +7182,11 @@
         <v>29</v>
       </c>
       <c r="E158" s="6">
-        <f>IF(AND($B158&lt;&gt;"", $G158&lt;&gt;"TBD"), ($B158-$G158)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F158" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="G158" s="9">
@@ -7187,11 +7208,11 @@
         <v>33</v>
       </c>
       <c r="E159" s="6">
-        <f>IF(AND($B159&lt;&gt;"", $G159&lt;&gt;"TBD"), ($B159-$G159)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>3.36666666666666</v>
       </c>
       <c r="F159" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G159" s="9">
@@ -7213,11 +7234,11 @@
         <v>39</v>
       </c>
       <c r="E160" s="6">
-        <f>IF(AND($B160&lt;&gt;"", $G160&lt;&gt;"TBD"), ($B160-$G160)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>5.3666666666666529</v>
       </c>
       <c r="F160" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G160" s="9">
@@ -7239,11 +7260,11 @@
         <v>42</v>
       </c>
       <c r="E161" s="6">
-        <f>IF(AND($B161&lt;&gt;"", $G161&lt;&gt;"TBD"), ($B161-$G161)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>7.3833333333333417</v>
       </c>
       <c r="F161" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G161" s="9">
@@ -7265,11 +7286,11 @@
         <v>44</v>
       </c>
       <c r="E162" s="6">
-        <f>IF(AND($B162&lt;&gt;"", $G162&lt;&gt;"TBD"), ($B162-$G162)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>9.3833333333333346</v>
       </c>
       <c r="F162" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G162" s="9">
@@ -7291,11 +7312,11 @@
         <v>45</v>
       </c>
       <c r="E163" s="6">
-        <f>IF(AND($B163&lt;&gt;"", $G163&lt;&gt;"TBD"), ($B163-$G163)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>11.383333333333328</v>
       </c>
       <c r="F163" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G163" s="9">
@@ -7317,11 +7338,11 @@
         <v>48</v>
       </c>
       <c r="E164" s="6">
-        <f>IF(AND($B164&lt;&gt;"", $G164&lt;&gt;"TBD"), ($B164-$G164)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>13.38333333333332</v>
       </c>
       <c r="F164" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G164" s="9">
@@ -7343,11 +7364,11 @@
         <v>49</v>
       </c>
       <c r="E165" s="6">
-        <f>IF(AND($B165&lt;&gt;"", $G165&lt;&gt;"TBD"), ($B165-$G165)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>15.400000000000009</v>
       </c>
       <c r="F165" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="G165" s="9">
@@ -7369,11 +7390,11 @@
         <v>51</v>
       </c>
       <c r="E166" s="6">
-        <f>IF(AND($B166&lt;&gt;"", $G166&lt;&gt;"TBD"), ($B166-$G166)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>17.416666666666618</v>
       </c>
       <c r="F166" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G166" s="9">
@@ -7395,11 +7416,11 @@
         <v>52</v>
       </c>
       <c r="E167" s="6">
-        <f>IF(AND($B167&lt;&gt;"", $G167&lt;&gt;"TBD"), ($B167-$G167)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>19.433333333333309</v>
       </c>
       <c r="F167" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G167" s="9">
@@ -7421,11 +7442,11 @@
         <v>54</v>
       </c>
       <c r="E168" s="6">
-        <f>IF(AND($B168&lt;&gt;"", $G168&lt;&gt;"TBD"), ($B168-$G168)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>21.449999999999996</v>
       </c>
       <c r="F168" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G168" s="9">
@@ -7447,11 +7468,11 @@
         <v>55</v>
       </c>
       <c r="E169" s="6">
-        <f>IF(AND($B169&lt;&gt;"", $G169&lt;&gt;"TBD"), ($B169-$G169)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>23.449999999999989</v>
       </c>
       <c r="F169" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="G169" s="9">
@@ -7473,11 +7494,11 @@
         <v>55</v>
       </c>
       <c r="E170" s="6">
-        <f>IF(AND($B170&lt;&gt;"", $G170&lt;&gt;"TBD"), ($B170-$G170)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>25.449999999999982</v>
       </c>
       <c r="F170" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G170" s="9">
@@ -7499,11 +7520,11 @@
         <v>55</v>
       </c>
       <c r="E171" s="6">
-        <f>IF(AND($B171&lt;&gt;"", $G171&lt;&gt;"TBD"), ($B171-$G171)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>27.466666666666669</v>
       </c>
       <c r="F171" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G171" s="9">
@@ -7525,11 +7546,11 @@
         <v>57</v>
       </c>
       <c r="E172" s="6">
-        <f>IF(AND($B172&lt;&gt;"", $G172&lt;&gt;"TBD"), ($B172-$G172)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>29.466666666666661</v>
       </c>
       <c r="F172" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G172" s="9">
@@ -7551,11 +7572,11 @@
         <v>58</v>
       </c>
       <c r="E173" s="6">
-        <f>IF(AND($B173&lt;&gt;"", $G173&lt;&gt;"TBD"), ($B173-$G173)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>31.48333333333327</v>
       </c>
       <c r="F173" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G173" s="9">
@@ -7577,11 +7598,11 @@
         <v>30</v>
       </c>
       <c r="E174" s="6">
-        <f>IF(AND($B174&lt;&gt;"", $G174&lt;&gt;"TBD"), ($B174-$G174)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F174" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G174" s="9">
@@ -7603,11 +7624,11 @@
         <v>35</v>
       </c>
       <c r="E175" s="6">
-        <f>IF(AND($B175&lt;&gt;"", $G175&lt;&gt;"TBD"), ($B175-$G175)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>2.9666666666666774</v>
       </c>
       <c r="F175" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G175" s="9">
@@ -7629,11 +7650,11 @@
         <v>41</v>
       </c>
       <c r="E176" s="6">
-        <f>IF(AND($B176&lt;&gt;"", $G176&lt;&gt;"TBD"), ($B176-$G176)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>4.9666666666666703</v>
       </c>
       <c r="F176" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G176" s="9">
@@ -7655,11 +7676,11 @@
         <v>44</v>
       </c>
       <c r="E177" s="6">
-        <f>IF(AND($B177&lt;&gt;"", $G177&lt;&gt;"TBD"), ($B177-$G177)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>6.9833333333333591</v>
       </c>
       <c r="F177" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G177" s="9">
@@ -7681,11 +7702,11 @@
         <v>44</v>
       </c>
       <c r="E178" s="6">
-        <f>IF(AND($B178&lt;&gt;"", $G178&lt;&gt;"TBD"), ($B178-$G178)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>8.983333333333352</v>
       </c>
       <c r="F178" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G178" s="9">
@@ -7707,11 +7728,11 @@
         <v>47</v>
       </c>
       <c r="E179" s="6">
-        <f>IF(AND($B179&lt;&gt;"", $G179&lt;&gt;"TBD"), ($B179-$G179)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>10.983333333333345</v>
       </c>
       <c r="F179" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G179" s="9">
@@ -7733,11 +7754,11 @@
         <v>49</v>
       </c>
       <c r="E180" s="6">
-        <f>IF(AND($B180&lt;&gt;"", $G180&lt;&gt;"TBD"), ($B180-$G180)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>12.983333333333338</v>
       </c>
       <c r="F180" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="G180" s="9">
@@ -7759,11 +7780,11 @@
         <v>49</v>
       </c>
       <c r="E181" s="6">
-        <f>IF(AND($B181&lt;&gt;"", $G181&lt;&gt;"TBD"), ($B181-$G181)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>15.000000000000027</v>
       </c>
       <c r="F181" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G181" s="9">
@@ -7785,11 +7806,11 @@
         <v>52</v>
       </c>
       <c r="E182" s="6">
-        <f>IF(AND($B182&lt;&gt;"", $G182&lt;&gt;"TBD"), ($B182-$G182)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>17.000000000000021</v>
       </c>
       <c r="F182" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G182" s="9">
@@ -7811,11 +7832,11 @@
         <v>52</v>
       </c>
       <c r="E183" s="6">
-        <f>IF(AND($B183&lt;&gt;"", $G183&lt;&gt;"TBD"), ($B183-$G183)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>19.000000000000014</v>
       </c>
       <c r="F183" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G183" s="9">
@@ -7837,11 +7858,11 @@
         <v>55</v>
       </c>
       <c r="E184" s="6">
-        <f>IF(AND($B184&lt;&gt;"", $G184&lt;&gt;"TBD"), ($B184-$G184)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>21.016666666666701</v>
       </c>
       <c r="F184" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G184" s="9">
@@ -7863,11 +7884,11 @@
         <v>55</v>
       </c>
       <c r="E185" s="6">
-        <f>IF(AND($B185&lt;&gt;"", $G185&lt;&gt;"TBD"), ($B185-$G185)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>23.033333333333388</v>
       </c>
       <c r="F185" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G185" s="9">
@@ -7889,11 +7910,11 @@
         <v>55</v>
       </c>
       <c r="E186" s="6">
-        <f>IF(AND($B186&lt;&gt;"", $G186&lt;&gt;"TBD"), ($B186-$G186)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>25.033333333333381</v>
       </c>
       <c r="F186" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G186" s="9">
@@ -7915,11 +7936,11 @@
         <v>55</v>
       </c>
       <c r="E187" s="6">
-        <f>IF(AND($B187&lt;&gt;"", $G187&lt;&gt;"TBD"), ($B187-$G187)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>27.033333333333374</v>
       </c>
       <c r="F187" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G187" s="9">
@@ -7941,11 +7962,11 @@
         <v>58</v>
       </c>
       <c r="E188" s="6">
-        <f>IF(AND($B188&lt;&gt;"", $G188&lt;&gt;"TBD"), ($B188-$G188)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>29.049999999999983</v>
       </c>
       <c r="F188" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="G188" s="9">
@@ -7967,11 +7988,11 @@
         <v>58</v>
       </c>
       <c r="E189" s="6">
-        <f>IF(AND($B189&lt;&gt;"", $G189&lt;&gt;"TBD"), ($B189-$G189)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>31.066666666666674</v>
       </c>
       <c r="F189" s="2">
-        <f t="shared" ref="F189:F267" si="3">IF(AND($D189&lt;&gt;"",$C189&lt;&gt;""), $D189-$C189, "")</f>
+        <f t="shared" ref="F189:F267" si="6">IF(AND($D189&lt;&gt;"",$C189&lt;&gt;""), $D189-$C189, "")</f>
         <v>3</v>
       </c>
       <c r="G189" s="9">
@@ -7993,11 +8014,11 @@
         <v>38</v>
       </c>
       <c r="E190" s="6">
-        <f>IF(AND($B190&lt;&gt;"", $G190&lt;&gt;"TBD"), ($B190-$G190)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>3.9999999999999858</v>
       </c>
       <c r="F190" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G190" s="9">
@@ -8019,11 +8040,11 @@
         <v>41</v>
       </c>
       <c r="E191" s="6">
-        <f>IF(AND($B191&lt;&gt;"", $G191&lt;&gt;"TBD"), ($B191-$G191)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>5.8499999999999552</v>
       </c>
       <c r="F191" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G191" s="9">
@@ -8045,11 +8066,11 @@
         <v>44</v>
       </c>
       <c r="E192" s="6">
-        <f>IF(AND($B192&lt;&gt;"", $G192&lt;&gt;"TBD"), ($B192-$G192)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>7.866666666666644</v>
       </c>
       <c r="F192" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G192" s="9">
@@ -8071,11 +8092,11 @@
         <v>47</v>
       </c>
       <c r="E193" s="6">
-        <f>IF(AND($B193&lt;&gt;"", $G193&lt;&gt;"TBD"), ($B193-$G193)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>9.8666666666666369</v>
       </c>
       <c r="F193" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G193" s="9">
@@ -8097,11 +8118,11 @@
         <v>49</v>
       </c>
       <c r="E194" s="6">
-        <f>IF(AND($B194&lt;&gt;"", $G194&lt;&gt;"TBD"), ($B194-$G194)*1440, "")</f>
+        <f t="shared" si="5"/>
         <v>13.883333333333319</v>
       </c>
       <c r="F194" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G194" s="9">
@@ -8123,11 +8144,11 @@
         <v>52</v>
       </c>
       <c r="E195" s="6">
-        <f>IF(AND($B195&lt;&gt;"", $G195&lt;&gt;"TBD"), ($B195-$G195)*1440, "")</f>
+        <f t="shared" ref="E195:E258" si="7">IF(AND($B195&lt;&gt;"", $G195&lt;&gt;"TBD"), ($B195-$G195)*1440, "")</f>
         <v>15.883333333333312</v>
       </c>
       <c r="F195" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G195" s="9">
@@ -8149,11 +8170,11 @@
         <v>52</v>
       </c>
       <c r="E196" s="6">
-        <f>IF(AND($B196&lt;&gt;"", $G196&lt;&gt;"TBD"), ($B196-$G196)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>17.899999999999999</v>
       </c>
       <c r="F196" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G196" s="9">
@@ -8175,11 +8196,11 @@
         <v>52</v>
       </c>
       <c r="E197" s="6">
-        <f>IF(AND($B197&lt;&gt;"", $G197&lt;&gt;"TBD"), ($B197-$G197)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>19.916666666666689</v>
       </c>
       <c r="F197" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G197" s="9">
@@ -8201,11 +8222,11 @@
         <v>55</v>
       </c>
       <c r="E198" s="6">
-        <f>IF(AND($B198&lt;&gt;"", $G198&lt;&gt;"TBD"), ($B198-$G198)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>21.916666666666682</v>
       </c>
       <c r="F198" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G198" s="9">
@@ -8227,11 +8248,11 @@
         <v>55</v>
       </c>
       <c r="E199" s="6">
-        <f>IF(AND($B199&lt;&gt;"", $G199&lt;&gt;"TBD"), ($B199-$G199)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>23.933333333333291</v>
       </c>
       <c r="F199" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G199" s="9">
@@ -8253,11 +8274,11 @@
         <v>55</v>
       </c>
       <c r="E200" s="6">
-        <f>IF(AND($B200&lt;&gt;"", $G200&lt;&gt;"TBD"), ($B200-$G200)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>25.949999999999982</v>
       </c>
       <c r="F200" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G200" s="9">
@@ -8279,11 +8300,11 @@
         <v>58</v>
       </c>
       <c r="E201" s="6">
-        <f>IF(AND($B201&lt;&gt;"", $G201&lt;&gt;"TBD"), ($B201-$G201)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>27.949999999999974</v>
       </c>
       <c r="F201" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G201" s="9">
@@ -8305,11 +8326,11 @@
         <v>58</v>
       </c>
       <c r="E202" s="6">
-        <f>IF(AND($B202&lt;&gt;"", $G202&lt;&gt;"TBD"), ($B202-$G202)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>29.966666666666661</v>
       </c>
       <c r="F202" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G202" s="9">
@@ -8331,11 +8352,11 @@
         <v>58</v>
       </c>
       <c r="E203" s="6">
-        <f>IF(AND($B203&lt;&gt;"", $G203&lt;&gt;"TBD"), ($B203-$G203)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>31.966666666666654</v>
       </c>
       <c r="F203" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G203" s="9">
@@ -8357,11 +8378,11 @@
         <v>58</v>
       </c>
       <c r="E204" s="6">
-        <f>IF(AND($B204&lt;&gt;"", $G204&lt;&gt;"TBD"), ($B204-$G204)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>33.966666666666647</v>
       </c>
       <c r="F204" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G204" s="9">
@@ -8383,11 +8404,11 @@
         <v>31</v>
       </c>
       <c r="E205" s="6">
-        <f>IF(AND($B205&lt;&gt;"", $G205&lt;&gt;"TBD"), ($B205-$G205)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>2.9999999999999893</v>
       </c>
       <c r="F205" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="G205" s="9">
@@ -8409,11 +8430,11 @@
         <v>33</v>
       </c>
       <c r="E206" s="6">
-        <f>IF(AND($B206&lt;&gt;"", $G206&lt;&gt;"TBD"), ($B206-$G206)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>3.383333333333276</v>
       </c>
       <c r="F206" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G206" s="9">
@@ -8435,11 +8456,11 @@
         <v>38</v>
       </c>
       <c r="E207" s="6">
-        <f>IF(AND($B207&lt;&gt;"", $G207&lt;&gt;"TBD"), ($B207-$G207)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>5.4000000000000448</v>
       </c>
       <c r="F207" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="G207" s="9">
@@ -8461,11 +8482,11 @@
         <v>41</v>
       </c>
       <c r="E208" s="6">
-        <f>IF(AND($B208&lt;&gt;"", $G208&lt;&gt;"TBD"), ($B208-$G208)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>7.4166666666666536</v>
       </c>
       <c r="F208" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="G208" s="9">
@@ -8487,11 +8508,11 @@
         <v>44</v>
       </c>
       <c r="E209" s="6">
-        <f>IF(AND($B209&lt;&gt;"", $G209&lt;&gt;"TBD"), ($B209-$G209)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>9.4333333333332625</v>
       </c>
       <c r="F209" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G209" s="9">
@@ -8513,11 +8534,11 @@
         <v>45</v>
       </c>
       <c r="E210" s="6">
-        <f>IF(AND($B210&lt;&gt;"", $G210&lt;&gt;"TBD"), ($B210-$G210)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>11.433333333333255</v>
       </c>
       <c r="F210" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G210" s="9">
@@ -8539,11 +8560,11 @@
         <v>47</v>
       </c>
       <c r="E211" s="6">
-        <f>IF(AND($B211&lt;&gt;"", $G211&lt;&gt;"TBD"), ($B211-$G211)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>13.450000000000024</v>
       </c>
       <c r="F211" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="G211" s="9">
@@ -8565,11 +8586,11 @@
         <v>49</v>
       </c>
       <c r="E212" s="6">
-        <f>IF(AND($B212&lt;&gt;"", $G212&lt;&gt;"TBD"), ($B212-$G212)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>15.450000000000017</v>
       </c>
       <c r="F212" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="G212" s="9">
@@ -8591,11 +8612,11 @@
         <v>49</v>
       </c>
       <c r="E213" s="6">
-        <f>IF(AND($B213&lt;&gt;"", $G213&lt;&gt;"TBD"), ($B213-$G213)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>17.466666666666626</v>
       </c>
       <c r="F213" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G213" s="9">
@@ -8617,11 +8638,11 @@
         <v>52</v>
       </c>
       <c r="E214" s="6">
-        <f>IF(AND($B214&lt;&gt;"", $G214&lt;&gt;"TBD"), ($B214-$G214)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>19.483333333333395</v>
       </c>
       <c r="F214" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G214" s="9">
@@ -8643,11 +8664,11 @@
         <v>52</v>
       </c>
       <c r="E215" s="6">
-        <f>IF(AND($B215&lt;&gt;"", $G215&lt;&gt;"TBD"), ($B215-$G215)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>21.483333333333388</v>
       </c>
       <c r="F215" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G215" s="9">
@@ -8669,11 +8690,11 @@
         <v>52</v>
       </c>
       <c r="E216" s="6">
-        <f>IF(AND($B216&lt;&gt;"", $G216&lt;&gt;"TBD"), ($B216-$G216)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>23.499999999999996</v>
       </c>
       <c r="F216" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G216" s="9">
@@ -8695,11 +8716,11 @@
         <v>55</v>
       </c>
       <c r="E217" s="6">
-        <f>IF(AND($B217&lt;&gt;"", $G217&lt;&gt;"TBD"), ($B217-$G217)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>25.499999999999989</v>
       </c>
       <c r="F217" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G217" s="9">
@@ -8721,11 +8742,11 @@
         <v>55</v>
       </c>
       <c r="E218" s="6">
-        <f>IF(AND($B218&lt;&gt;"", $G218&lt;&gt;"TBD"), ($B218-$G218)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>27.499999999999982</v>
       </c>
       <c r="F218" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G218" s="9">
@@ -8747,11 +8768,11 @@
         <v>55</v>
       </c>
       <c r="E219" s="6">
-        <f>IF(AND($B219&lt;&gt;"", $G219&lt;&gt;"TBD"), ($B219-$G219)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>29.499999999999975</v>
       </c>
       <c r="F219" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G219" s="9">
@@ -8773,11 +8794,11 @@
         <v>55</v>
       </c>
       <c r="E220" s="6">
-        <f>IF(AND($B220&lt;&gt;"", $G220&lt;&gt;"TBD"), ($B220-$G220)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>31.499999999999968</v>
       </c>
       <c r="F220" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G220" s="9">
@@ -8799,11 +8820,11 @@
         <v>30</v>
       </c>
       <c r="E221" s="6">
-        <f>IF(AND($B221&lt;&gt;"", $G221&lt;&gt;"TBD"), ($B221-$G221)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F221" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G221" s="9">
@@ -8825,11 +8846,11 @@
         <v>35</v>
       </c>
       <c r="E222" s="6">
-        <f>IF(AND($B222&lt;&gt;"", $G222&lt;&gt;"TBD"), ($B222-$G222)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>1.5500000000000025</v>
       </c>
       <c r="F222" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="G222" s="9">
@@ -8851,11 +8872,11 @@
         <v>39</v>
       </c>
       <c r="E223" s="6">
-        <f>IF(AND($B223&lt;&gt;"", $G223&lt;&gt;"TBD"), ($B223-$G223)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>3.5666666666666913</v>
       </c>
       <c r="F223" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G223" s="9">
@@ -8877,11 +8898,11 @@
         <v>42</v>
       </c>
       <c r="E224" s="6">
-        <f>IF(AND($B224&lt;&gt;"", $G224&lt;&gt;"TBD"), ($B224-$G224)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>5.5666666666666842</v>
       </c>
       <c r="F224" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G224" s="9">
@@ -8903,11 +8924,11 @@
         <v>44</v>
       </c>
       <c r="E225" s="6">
-        <f>IF(AND($B225&lt;&gt;"", $G225&lt;&gt;"TBD"), ($B225-$G225)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>7.583333333333373</v>
       </c>
       <c r="F225" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G225" s="9">
@@ -8929,11 +8950,11 @@
         <v>47</v>
       </c>
       <c r="E226" s="6">
-        <f>IF(AND($B226&lt;&gt;"", $G226&lt;&gt;"TBD"), ($B226-$G226)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>9.6000000000000618</v>
       </c>
       <c r="F226" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G226" s="9">
@@ -8955,11 +8976,11 @@
         <v>49</v>
       </c>
       <c r="E227" s="6">
-        <f>IF(AND($B227&lt;&gt;"", $G227&lt;&gt;"TBD"), ($B227-$G227)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>11.600000000000055</v>
       </c>
       <c r="F227" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="G227" s="9">
@@ -8981,11 +9002,11 @@
         <v>49</v>
       </c>
       <c r="E228" s="6">
-        <f>IF(AND($B228&lt;&gt;"", $G228&lt;&gt;"TBD"), ($B228-$G228)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>13.616666666666664</v>
       </c>
       <c r="F228" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G228" s="9">
@@ -9007,11 +9028,11 @@
         <v>52</v>
       </c>
       <c r="E229" s="6">
-        <f>IF(AND($B229&lt;&gt;"", $G229&lt;&gt;"TBD"), ($B229-$G229)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>15.633333333333352</v>
       </c>
       <c r="F229" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="G229" s="9">
@@ -9033,11 +9054,11 @@
         <v>52</v>
       </c>
       <c r="E230" s="6">
-        <f>IF(AND($B230&lt;&gt;"", $G230&lt;&gt;"TBD"), ($B230-$G230)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>17.633333333333347</v>
       </c>
       <c r="F230" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G230" s="9">
@@ -9059,11 +9080,11 @@
         <v>52</v>
       </c>
       <c r="E231" s="6">
-        <f>IF(AND($B231&lt;&gt;"", $G231&lt;&gt;"TBD"), ($B231-$G231)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>19.63333333333334</v>
       </c>
       <c r="F231" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G231" s="9">
@@ -9085,11 +9106,11 @@
         <v>55</v>
       </c>
       <c r="E232" s="6">
-        <f>IF(AND($B232&lt;&gt;"", $G232&lt;&gt;"TBD"), ($B232-$G232)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>21.650000000000027</v>
       </c>
       <c r="F232" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G232" s="9">
@@ -9111,11 +9132,11 @@
         <v>55</v>
       </c>
       <c r="E233" s="6">
-        <f>IF(AND($B233&lt;&gt;"", $G233&lt;&gt;"TBD"), ($B233-$G233)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>23.65000000000002</v>
       </c>
       <c r="F233" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G233" s="9">
@@ -9137,11 +9158,11 @@
         <v>55</v>
       </c>
       <c r="E234" s="6">
-        <f>IF(AND($B234&lt;&gt;"", $G234&lt;&gt;"TBD"), ($B234-$G234)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>25.650000000000013</v>
       </c>
       <c r="F234" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G234" s="9">
@@ -9163,11 +9184,11 @@
         <v>58</v>
       </c>
       <c r="E235" s="6">
-        <f>IF(AND($B235&lt;&gt;"", $G235&lt;&gt;"TBD"), ($B235-$G235)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>27.6666666666667</v>
       </c>
       <c r="F235" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="G235" s="9">
@@ -9189,11 +9210,11 @@
         <v>58</v>
       </c>
       <c r="E236" s="6">
-        <f>IF(AND($B236&lt;&gt;"", $G236&lt;&gt;"TBD"), ($B236-$G236)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>29.68333333333339</v>
       </c>
       <c r="F236" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G236" s="9">
@@ -9215,11 +9236,11 @@
         <v>39</v>
       </c>
       <c r="E237" s="6">
-        <f>IF(AND($B237&lt;&gt;"", $G237&lt;&gt;"TBD"), ($B237-$G237)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>4.0000000000000657</v>
       </c>
       <c r="F237" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G237" s="9">
@@ -9241,11 +9262,11 @@
         <v>41</v>
       </c>
       <c r="E238" s="6">
-        <f>IF(AND($B238&lt;&gt;"", $G238&lt;&gt;"TBD"), ($B238-$G238)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>6.0833333333333783</v>
       </c>
       <c r="F238" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G238" s="9">
@@ -9267,11 +9288,11 @@
         <v>42</v>
       </c>
       <c r="E239" s="6">
-        <f>IF(AND($B239&lt;&gt;"", $G239&lt;&gt;"TBD"), ($B239-$G239)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>8.1000000000000671</v>
       </c>
       <c r="F239" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G239" s="9">
@@ -9293,11 +9314,11 @@
         <v>45</v>
       </c>
       <c r="E240" s="6">
-        <f>IF(AND($B240&lt;&gt;"", $G240&lt;&gt;"TBD"), ($B240-$G240)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>10.10000000000006</v>
       </c>
       <c r="F240" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G240" s="9">
@@ -9319,11 +9340,11 @@
         <v>47</v>
       </c>
       <c r="E241" s="6">
-        <f>IF(AND($B241&lt;&gt;"", $G241&lt;&gt;"TBD"), ($B241-$G241)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>12.100000000000053</v>
       </c>
       <c r="F241" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G241" s="9">
@@ -9345,11 +9366,11 @@
         <v>49</v>
       </c>
       <c r="E242" s="6">
-        <f>IF(AND($B242&lt;&gt;"", $G242&lt;&gt;"TBD"), ($B242-$G242)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>14.100000000000046</v>
       </c>
       <c r="F242" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="G242" s="9">
@@ -9371,11 +9392,11 @@
         <v>51</v>
       </c>
       <c r="E243" s="6">
-        <f>IF(AND($B243&lt;&gt;"", $G243&lt;&gt;"TBD"), ($B243-$G243)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>16.116666666666735</v>
       </c>
       <c r="F243" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G243" s="9">
@@ -9397,11 +9418,11 @@
         <v>52</v>
       </c>
       <c r="E244" s="6">
-        <f>IF(AND($B244&lt;&gt;"", $G244&lt;&gt;"TBD"), ($B244-$G244)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>18.116666666666728</v>
       </c>
       <c r="F244" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G244" s="9">
@@ -9423,11 +9444,11 @@
         <v>52</v>
       </c>
       <c r="E245" s="6">
-        <f>IF(AND($B245&lt;&gt;"", $G245&lt;&gt;"TBD"), ($B245-$G245)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>20.11666666666672</v>
       </c>
       <c r="F245" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G245" s="9">
@@ -9449,11 +9470,11 @@
         <v>54</v>
       </c>
       <c r="E246" s="6">
-        <f>IF(AND($B246&lt;&gt;"", $G246&lt;&gt;"TBD"), ($B246-$G246)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>22.133333333333329</v>
       </c>
       <c r="F246" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G246" s="9">
@@ -9475,11 +9496,11 @@
         <v>55</v>
       </c>
       <c r="E247" s="6">
-        <f>IF(AND($B247&lt;&gt;"", $G247&lt;&gt;"TBD"), ($B247-$G247)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>24.133333333333404</v>
       </c>
       <c r="F247" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G247" s="9">
@@ -9501,11 +9522,11 @@
         <v>55</v>
       </c>
       <c r="E248" s="6">
-        <f>IF(AND($B248&lt;&gt;"", $G248&lt;&gt;"TBD"), ($B248-$G248)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>26.133333333333397</v>
       </c>
       <c r="F248" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G248" s="9">
@@ -9527,11 +9548,11 @@
         <v>57</v>
       </c>
       <c r="E249" s="6">
-        <f>IF(AND($B249&lt;&gt;"", $G249&lt;&gt;"TBD"), ($B249-$G249)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>28.150000000000006</v>
       </c>
       <c r="F249" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G249" s="9">
@@ -9553,11 +9574,11 @@
         <v>58</v>
       </c>
       <c r="E250" s="6">
-        <f>IF(AND($B250&lt;&gt;"", $G250&lt;&gt;"TBD"), ($B250-$G250)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>30.166666666666693</v>
       </c>
       <c r="F250" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G250" s="9">
@@ -9579,11 +9600,11 @@
         <v>58</v>
       </c>
       <c r="E251" s="6">
-        <f>IF(AND($B251&lt;&gt;"", $G251&lt;&gt;"TBD"), ($B251-$G251)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>32.166666666666686</v>
       </c>
       <c r="F251" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G251" s="9">
@@ -9605,11 +9626,11 @@
         <v>58</v>
       </c>
       <c r="E252" s="6">
-        <f>IF(AND($B252&lt;&gt;"", $G252&lt;&gt;"TBD"), ($B252-$G252)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>34.183333333333373</v>
       </c>
       <c r="F252" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G252" s="9">
@@ -9631,11 +9652,11 @@
         <v>31</v>
       </c>
       <c r="E253" s="6">
-        <f>IF(AND($B253&lt;&gt;"", $G253&lt;&gt;"TBD"), ($B253-$G253)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F253" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G253" s="9">
@@ -9657,11 +9678,11 @@
         <v>33</v>
       </c>
       <c r="E254" s="6">
-        <f>IF(AND($B254&lt;&gt;"", $G254&lt;&gt;"TBD"), ($B254-$G254)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>2.8333333333333499</v>
       </c>
       <c r="F254" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G254" s="9">
@@ -9684,11 +9705,11 @@
         <v>39</v>
       </c>
       <c r="E255" s="6">
-        <f>IF(AND($B255&lt;&gt;"", $G255&lt;&gt;"TBD"), ($B255-$G255)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>4.8333333333333428</v>
       </c>
       <c r="F255" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G255" s="9">
@@ -9710,11 +9731,11 @@
         <v>42</v>
       </c>
       <c r="E256" s="6">
-        <f>IF(AND($B256&lt;&gt;"", $G256&lt;&gt;"TBD"), ($B256-$G256)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>6.8333333333333357</v>
       </c>
       <c r="F256" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G256" s="9">
@@ -9736,11 +9757,11 @@
         <v>44</v>
       </c>
       <c r="E257" s="6">
-        <f>IF(AND($B257&lt;&gt;"", $G257&lt;&gt;"TBD"), ($B257-$G257)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>8.8333333333333286</v>
       </c>
       <c r="F257" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G257" s="9">
@@ -9762,11 +9783,11 @@
         <v>45</v>
       </c>
       <c r="E258" s="6">
-        <f>IF(AND($B258&lt;&gt;"", $G258&lt;&gt;"TBD"), ($B258-$G258)*1440, "")</f>
+        <f t="shared" si="7"/>
         <v>10.850000000000097</v>
       </c>
       <c r="F258" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G258" s="9">
@@ -9788,11 +9809,11 @@
         <v>48</v>
       </c>
       <c r="E259" s="6">
-        <f>IF(AND($B259&lt;&gt;"", $G259&lt;&gt;"TBD"), ($B259-$G259)*1440, "")</f>
+        <f t="shared" ref="E259:E317" si="8">IF(AND($B259&lt;&gt;"", $G259&lt;&gt;"TBD"), ($B259-$G259)*1440, "")</f>
         <v>12.85000000000009</v>
       </c>
       <c r="F259" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G259" s="9">
@@ -9814,11 +9835,11 @@
         <v>49</v>
       </c>
       <c r="E260" s="6">
-        <f>IF(AND($B260&lt;&gt;"", $G260&lt;&gt;"TBD"), ($B260-$G260)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>14.866666666666699</v>
       </c>
       <c r="F260" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="G260" s="9">
@@ -9840,11 +9861,11 @@
         <v>51</v>
       </c>
       <c r="E261" s="6">
-        <f>IF(AND($B261&lt;&gt;"", $G261&lt;&gt;"TBD"), ($B261-$G261)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>16.866666666666692</v>
       </c>
       <c r="F261" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G261" s="9">
@@ -9866,11 +9887,11 @@
         <v>52</v>
       </c>
       <c r="E262" s="6">
-        <f>IF(AND($B262&lt;&gt;"", $G262&lt;&gt;"TBD"), ($B262-$G262)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>18.883333333333461</v>
       </c>
       <c r="F262" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G262" s="9">
@@ -9892,11 +9913,11 @@
         <v>54</v>
       </c>
       <c r="E263" s="6">
-        <f>IF(AND($B263&lt;&gt;"", $G263&lt;&gt;"TBD"), ($B263-$G263)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>20.883333333333454</v>
       </c>
       <c r="F263" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G263" s="9">
@@ -9918,11 +9939,11 @@
         <v>55</v>
       </c>
       <c r="E264" s="6">
-        <f>IF(AND($B264&lt;&gt;"", $G264&lt;&gt;"TBD"), ($B264-$G264)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>22.883333333333447</v>
       </c>
       <c r="F264" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="G264" s="9">
@@ -9944,11 +9965,11 @@
         <v>55</v>
       </c>
       <c r="E265" s="6">
-        <f>IF(AND($B265&lt;&gt;"", $G265&lt;&gt;"TBD"), ($B265-$G265)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>24.900000000000055</v>
       </c>
       <c r="F265" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G265" s="9">
@@ -9970,11 +9991,11 @@
         <v>55</v>
       </c>
       <c r="E266" s="6">
-        <f>IF(AND($B266&lt;&gt;"", $G266&lt;&gt;"TBD"), ($B266-$G266)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>26.900000000000048</v>
       </c>
       <c r="F266" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G266" s="9">
@@ -9996,11 +10017,11 @@
         <v>57</v>
       </c>
       <c r="E267" s="6">
-        <f>IF(AND($B267&lt;&gt;"", $G267&lt;&gt;"TBD"), ($B267-$G267)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>28.900000000000041</v>
       </c>
       <c r="F267" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="G267" s="9">
@@ -10022,11 +10043,11 @@
         <v>58</v>
       </c>
       <c r="E268" s="6">
-        <f>IF(AND($B268&lt;&gt;"", $G268&lt;&gt;"TBD"), ($B268-$G268)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>30.900000000000034</v>
       </c>
       <c r="F268" s="2">
-        <f t="shared" ref="F268:F296" si="4">IF(AND(D268&lt;&gt;"",C268&lt;&gt;""),D268-C268,"")</f>
+        <f t="shared" ref="F268:F296" si="9">IF(AND(D268&lt;&gt;"",C268&lt;&gt;""),D268-C268,"")</f>
         <v>4</v>
       </c>
       <c r="G268" s="9">
@@ -10048,11 +10069,11 @@
         <v>31</v>
       </c>
       <c r="E269" s="6">
-        <f>IF(AND($B269&lt;&gt;"", $G269&lt;&gt;"TBD"), ($B269-$G269)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>0.99999999999999645</v>
       </c>
       <c r="F269" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="G269" s="9">
@@ -10074,11 +10095,11 @@
         <v>49</v>
       </c>
       <c r="E270" s="6">
-        <f>IF(AND($B270&lt;&gt;"", $G270&lt;&gt;"TBD"), ($B270-$G270)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>14.816666666666691</v>
       </c>
       <c r="F270" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G270" s="9">
@@ -10100,11 +10121,11 @@
         <v>52</v>
       </c>
       <c r="E271" s="6">
-        <f>IF(AND($B271&lt;&gt;"", $G271&lt;&gt;"TBD"), ($B271-$G271)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>16.816666666666684</v>
       </c>
       <c r="F271" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G271" s="9">
@@ -10126,11 +10147,11 @@
         <v>52</v>
       </c>
       <c r="E272" s="6">
-        <f>IF(AND($B272&lt;&gt;"", $G272&lt;&gt;"TBD"), ($B272-$G272)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>18.816666666666677</v>
       </c>
       <c r="F272" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G272" s="9">
@@ -10152,11 +10173,11 @@
         <v>52</v>
       </c>
       <c r="E273" s="6">
-        <f>IF(AND($B273&lt;&gt;"", $G273&lt;&gt;"TBD"), ($B273-$G273)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>20.833333333333286</v>
       </c>
       <c r="F273" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G273" s="9">
@@ -10178,11 +10199,11 @@
         <v>55</v>
       </c>
       <c r="E274" s="6">
-        <f>IF(AND($B274&lt;&gt;"", $G274&lt;&gt;"TBD"), ($B274-$G274)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>22.850000000000055</v>
       </c>
       <c r="F274" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G274" s="9">
@@ -10204,11 +10225,11 @@
         <v>55</v>
       </c>
       <c r="E275" s="6">
-        <f>IF(AND($B275&lt;&gt;"", $G275&lt;&gt;"TBD"), ($B275-$G275)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>24.850000000000048</v>
       </c>
       <c r="F275" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G275" s="9">
@@ -10230,11 +10251,11 @@
         <v>55</v>
       </c>
       <c r="E276" s="6">
-        <f>IF(AND($B276&lt;&gt;"", $G276&lt;&gt;"TBD"), ($B276-$G276)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>26.866666666666656</v>
       </c>
       <c r="F276" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G276" s="9">
@@ -10256,11 +10277,11 @@
         <v>55</v>
       </c>
       <c r="E277" s="6">
-        <f>IF(AND($B277&lt;&gt;"", $G277&lt;&gt;"TBD"), ($B277-$G277)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>28.883333333333265</v>
       </c>
       <c r="F277" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G277" s="9">
@@ -10282,11 +10303,11 @@
         <v>58</v>
       </c>
       <c r="E278" s="6">
-        <f>IF(AND($B278&lt;&gt;"", $G278&lt;&gt;"TBD"), ($B278-$G278)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>30.883333333333258</v>
       </c>
       <c r="F278" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="G278" s="9">
@@ -10308,11 +10329,11 @@
         <v>58</v>
       </c>
       <c r="E279" s="6">
-        <f>IF(AND($B279&lt;&gt;"", $G279&lt;&gt;"TBD"), ($B279-$G279)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>32.900000000000027</v>
       </c>
       <c r="F279" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G279" s="9">
@@ -10334,11 +10355,11 @@
         <v>58</v>
       </c>
       <c r="E280" s="6">
-        <f>IF(AND($B280&lt;&gt;"", $G280&lt;&gt;"TBD"), ($B280-$G280)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>34.916666666666636</v>
       </c>
       <c r="F280" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G280" s="9">
@@ -10360,11 +10381,11 @@
         <v>58</v>
       </c>
       <c r="E281" s="6">
-        <f>IF(AND($B281&lt;&gt;"", $G281&lt;&gt;"TBD"), ($B281-$G281)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>36.933333333333408</v>
       </c>
       <c r="F281" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G281" s="9">
@@ -10386,11 +10407,11 @@
         <v>58</v>
       </c>
       <c r="E282" s="6">
-        <f>IF(AND($B282&lt;&gt;"", $G282&lt;&gt;"TBD"), ($B282-$G282)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>38.933333333333394</v>
       </c>
       <c r="F282" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G282" s="9">
@@ -10412,11 +10433,11 @@
         <v>58</v>
       </c>
       <c r="E283" s="6">
-        <f>IF(AND($B283&lt;&gt;"", $G283&lt;&gt;"TBD"), ($B283-$G283)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>40.950000000000003</v>
       </c>
       <c r="F283" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G283" s="9">
@@ -10438,11 +10459,11 @@
         <v>61</v>
       </c>
       <c r="E284" s="6">
-        <f>IF(AND($B284&lt;&gt;"", $G284&lt;&gt;"TBD"), ($B284-$G284)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>42.95</v>
       </c>
       <c r="F284" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="G284" s="9">
@@ -10464,11 +10485,11 @@
         <v>30</v>
       </c>
       <c r="E285" s="6">
-        <f>IF(AND($B285&lt;&gt;"", $G285&lt;&gt;"TBD"), ($B285-$G285)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F285" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G285" s="9">
@@ -10490,11 +10511,11 @@
         <v>33</v>
       </c>
       <c r="E286" s="6">
-        <f>IF(AND($B286&lt;&gt;"", $G286&lt;&gt;"TBD"), ($B286-$G286)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>3.7166666666666348</v>
       </c>
       <c r="F286" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G286" s="9">
@@ -10516,11 +10537,11 @@
         <v>38</v>
       </c>
       <c r="E287" s="6">
-        <f>IF(AND($B287&lt;&gt;"", $G287&lt;&gt;"TBD"), ($B287-$G287)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>5.7166666666666277</v>
       </c>
       <c r="F287" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G287" s="9">
@@ -10542,11 +10563,11 @@
         <v>41</v>
       </c>
       <c r="E288" s="6">
-        <f>IF(AND($B288&lt;&gt;"", $G288&lt;&gt;"TBD"), ($B288-$G288)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>7.7333333333333165</v>
       </c>
       <c r="F288" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G288" s="9">
@@ -10568,11 +10589,11 @@
         <v>42</v>
       </c>
       <c r="E289" s="6">
-        <f>IF(AND($B289&lt;&gt;"", $G289&lt;&gt;"TBD"), ($B289-$G289)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>9.7333333333333094</v>
       </c>
       <c r="F289" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G289" s="9">
@@ -10594,11 +10615,11 @@
         <v>45</v>
       </c>
       <c r="E290" s="6">
-        <f>IF(AND($B290&lt;&gt;"", $G290&lt;&gt;"TBD"), ($B290-$G290)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>11.733333333333302</v>
       </c>
       <c r="F290" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G290" s="9">
@@ -10620,11 +10641,11 @@
         <v>47</v>
       </c>
       <c r="E291" s="6">
-        <f>IF(AND($B291&lt;&gt;"", $G291&lt;&gt;"TBD"), ($B291-$G291)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>13.733333333333295</v>
       </c>
       <c r="F291" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G291" s="9">
@@ -10646,11 +10667,11 @@
         <v>49</v>
       </c>
       <c r="E292" s="6">
-        <f>IF(AND($B292&lt;&gt;"", $G292&lt;&gt;"TBD"), ($B292-$G292)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>15.733333333333288</v>
       </c>
       <c r="F292" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="G292" s="9">
@@ -10672,11 +10693,11 @@
         <v>49</v>
       </c>
       <c r="E293" s="6">
-        <f>IF(AND($B293&lt;&gt;"", $G293&lt;&gt;"TBD"), ($B293-$G293)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>17.749999999999897</v>
       </c>
       <c r="F293" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G293" s="9">
@@ -10698,11 +10719,11 @@
         <v>51</v>
       </c>
       <c r="E294" s="6">
-        <f>IF(AND($B294&lt;&gt;"", $G294&lt;&gt;"TBD"), ($B294-$G294)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>19.74999999999989</v>
       </c>
       <c r="F294" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G294" s="9">
@@ -10724,11 +10745,11 @@
         <v>52</v>
       </c>
       <c r="E295" s="6">
-        <f>IF(AND($B295&lt;&gt;"", $G295&lt;&gt;"TBD"), ($B295-$G295)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>21.766666666666659</v>
       </c>
       <c r="F295" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G295" s="9">
@@ -10750,11 +10771,11 @@
         <v>54</v>
       </c>
       <c r="E296" s="6">
-        <f>IF(AND($B296&lt;&gt;"", $G296&lt;&gt;"TBD"), ($B296-$G296)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>23.766666666666652</v>
       </c>
       <c r="F296" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G296" s="9">
@@ -10776,11 +10797,11 @@
         <v>55</v>
       </c>
       <c r="E297" s="6">
-        <f>IF(AND($B297&lt;&gt;"", $G297&lt;&gt;"TBD"), ($B297-$G297)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>25.78333333333326</v>
       </c>
       <c r="F297" s="2">
-        <f t="shared" ref="F297:F346" si="5">IF(AND(D297&lt;&gt;"",C297&lt;&gt;""),D297-C297,"")</f>
+        <f t="shared" ref="F297:F346" si="10">IF(AND(D297&lt;&gt;"",C297&lt;&gt;""),D297-C297,"")</f>
         <v>4</v>
       </c>
       <c r="G297" s="9">
@@ -10802,11 +10823,11 @@
         <v>55</v>
       </c>
       <c r="E298" s="6">
-        <f>IF(AND($B298&lt;&gt;"", $G298&lt;&gt;"TBD"), ($B298-$G298)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>27.783333333333253</v>
       </c>
       <c r="F298" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G298" s="9">
@@ -10828,11 +10849,11 @@
         <v>55</v>
       </c>
       <c r="E299" s="6">
-        <f>IF(AND($B299&lt;&gt;"", $G299&lt;&gt;"TBD"), ($B299-$G299)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>29.783333333333246</v>
       </c>
       <c r="F299" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G299" s="9">
@@ -10854,11 +10875,11 @@
         <v>57</v>
       </c>
       <c r="E300" s="6">
-        <f>IF(AND($B300&lt;&gt;"", $G300&lt;&gt;"TBD"), ($B300-$G300)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>31.800000000000015</v>
       </c>
       <c r="F300" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G300" s="9">
@@ -10880,11 +10901,11 @@
         <v>29</v>
       </c>
       <c r="E301" s="6">
-        <f>IF(AND($B301&lt;&gt;"", $G301&lt;&gt;"TBD"), ($B301-$G301)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F301" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="G301" s="9">
@@ -10906,11 +10927,11 @@
         <v>32</v>
       </c>
       <c r="E302" s="6">
-        <f>IF(AND($B302&lt;&gt;"", $G302&lt;&gt;"TBD"), ($B302-$G302)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>3.0499999999999972</v>
       </c>
       <c r="F302" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G302" s="9">
@@ -10932,11 +10953,11 @@
         <v>38</v>
       </c>
       <c r="E303" s="6">
-        <f>IF(AND($B303&lt;&gt;"", $G303&lt;&gt;"TBD"), ($B303-$G303)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>5.066666666666686</v>
       </c>
       <c r="F303" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G303" s="9">
@@ -10958,11 +10979,11 @@
         <v>41</v>
       </c>
       <c r="E304" s="6">
-        <f>IF(AND($B304&lt;&gt;"", $G304&lt;&gt;"TBD"), ($B304-$G304)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>7.0666666666666789</v>
       </c>
       <c r="F304" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G304" s="9">
@@ -10984,11 +11005,11 @@
         <v>42</v>
       </c>
       <c r="E305" s="6">
-        <f>IF(AND($B305&lt;&gt;"", $G305&lt;&gt;"TBD"), ($B305-$G305)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>9.0833333333332877</v>
       </c>
       <c r="F305" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G305" s="9">
@@ -11010,11 +11031,11 @@
         <v>45</v>
       </c>
       <c r="E306" s="6">
-        <f>IF(AND($B306&lt;&gt;"", $G306&lt;&gt;"TBD"), ($B306-$G306)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>11.099999999999977</v>
       </c>
       <c r="F306" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G306" s="9">
@@ -11036,11 +11057,11 @@
         <v>47</v>
       </c>
       <c r="E307" s="6">
-        <f>IF(AND($B307&lt;&gt;"", $G307&lt;&gt;"TBD"), ($B307-$G307)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>13.099999999999969</v>
       </c>
       <c r="F307" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G307" s="9">
@@ -11062,11 +11083,11 @@
         <v>48</v>
       </c>
       <c r="E308" s="6">
-        <f>IF(AND($B308&lt;&gt;"", $G308&lt;&gt;"TBD"), ($B308-$G308)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>15.099999999999962</v>
       </c>
       <c r="F308" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G308" s="9">
@@ -11088,11 +11109,11 @@
         <v>49</v>
       </c>
       <c r="E309" s="6">
-        <f>IF(AND($B309&lt;&gt;"", $G309&lt;&gt;"TBD"), ($B309-$G309)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>17.099999999999955</v>
       </c>
       <c r="F309" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G309" s="9">
@@ -11114,11 +11135,11 @@
         <v>51</v>
       </c>
       <c r="E310" s="6">
-        <f>IF(AND($B310&lt;&gt;"", $G310&lt;&gt;"TBD"), ($B310-$G310)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>19.116666666666646</v>
       </c>
       <c r="F310" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G310" s="9">
@@ -11140,11 +11161,11 @@
         <v>52</v>
       </c>
       <c r="E311" s="6">
-        <f>IF(AND($B311&lt;&gt;"", $G311&lt;&gt;"TBD"), ($B311-$G311)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>21.116666666666639</v>
       </c>
       <c r="F311" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G311" s="9">
@@ -11166,11 +11187,11 @@
         <v>54</v>
       </c>
       <c r="E312" s="6">
-        <f>IF(AND($B312&lt;&gt;"", $G312&lt;&gt;"TBD"), ($B312-$G312)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>23.133333333333326</v>
       </c>
       <c r="F312" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G312" s="9">
@@ -11192,11 +11213,11 @@
         <v>54</v>
       </c>
       <c r="E313" s="6">
-        <f>IF(AND($B313&lt;&gt;"", $G313&lt;&gt;"TBD"), ($B313-$G313)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>25.150000000000013</v>
       </c>
       <c r="F313" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="G313" s="9">
@@ -11218,11 +11239,11 @@
         <v>55</v>
       </c>
       <c r="E314" s="6">
-        <f>IF(AND($B314&lt;&gt;"", $G314&lt;&gt;"TBD"), ($B314-$G314)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>27.150000000000006</v>
       </c>
       <c r="F314" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G314" s="9">
@@ -11244,11 +11265,11 @@
         <v>57</v>
       </c>
       <c r="E315" s="6">
-        <f>IF(AND($B315&lt;&gt;"", $G315&lt;&gt;"TBD"), ($B315-$G315)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>29.166666666666615</v>
       </c>
       <c r="F315" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G315" s="9">
@@ -11270,11 +11291,11 @@
         <v>57</v>
       </c>
       <c r="E316" s="6">
-        <f>IF(AND($B316&lt;&gt;"", $G316&lt;&gt;"TBD"), ($B316-$G316)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>31.183333333333305</v>
       </c>
       <c r="F316" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G316" s="9">
@@ -11296,11 +11317,11 @@
         <v>30</v>
       </c>
       <c r="E317" s="6">
-        <f>IF(AND($B317&lt;&gt;"", $G317&lt;&gt;"TBD"), ($B317-$G317)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F317" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G317" s="9">
@@ -11323,11 +11344,11 @@
         <v>33</v>
       </c>
       <c r="E318" s="6">
-        <f>IF(AND($B318&lt;&gt;"", $G318&lt;&gt;""), ($B318-$G318)*1440, "")</f>
+        <f t="shared" ref="E318:E332" si="11">IF(AND($B318&lt;&gt;"", $G318&lt;&gt;""), ($B318-$G318)*1440, "")</f>
         <v>3.2999999999998764</v>
       </c>
       <c r="F318" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G318" s="9">
@@ -11349,11 +11370,11 @@
         <v>38</v>
       </c>
       <c r="E319" s="6">
-        <f>IF(AND($B319&lt;&gt;"", $G319&lt;&gt;""), ($B319-$G319)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>5.2999999999998693</v>
       </c>
       <c r="F319" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G319" s="9">
@@ -11375,11 +11396,11 @@
         <v>41</v>
       </c>
       <c r="E320" s="6">
-        <f>IF(AND($B320&lt;&gt;"", $G320&lt;&gt;""), ($B320-$G320)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>7.2999999999998622</v>
       </c>
       <c r="F320" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G320" s="9">
@@ -11401,11 +11422,11 @@
         <v>44</v>
       </c>
       <c r="E321" s="6">
-        <f>IF(AND($B321&lt;&gt;"", $G321&lt;&gt;""), ($B321-$G321)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>9.3166666666666309</v>
       </c>
       <c r="F321" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G321" s="9">
@@ -11427,11 +11448,11 @@
         <v>45</v>
       </c>
       <c r="E322" s="6">
-        <f>IF(AND($B322&lt;&gt;"", $G322&lt;&gt;""), ($B322-$G322)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>11.33333333333324</v>
       </c>
       <c r="F322" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G322" s="9">
@@ -11453,11 +11474,11 @@
         <v>47</v>
       </c>
       <c r="E323" s="6">
-        <f>IF(AND($B323&lt;&gt;"", $G323&lt;&gt;""), ($B323-$G323)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>13.333333333333233</v>
       </c>
       <c r="F323" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G323" s="9">
@@ -11479,11 +11500,11 @@
         <v>49</v>
       </c>
       <c r="E324" s="6">
-        <f>IF(AND($B324&lt;&gt;"", $G324&lt;&gt;""), ($B324-$G324)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>15.350000000000001</v>
       </c>
       <c r="F324" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="G324" s="9">
@@ -11505,11 +11526,11 @@
         <v>49</v>
       </c>
       <c r="E325" s="6">
-        <f>IF(AND($B325&lt;&gt;"", $G325&lt;&gt;""), ($B325-$G325)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>17.349999999999994</v>
       </c>
       <c r="F325" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G325" s="9">
@@ -11531,11 +11552,11 @@
         <v>52</v>
       </c>
       <c r="E326" s="6">
-        <f>IF(AND($B326&lt;&gt;"", $G326&lt;&gt;""), ($B326-$G326)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>19.349999999999987</v>
       </c>
       <c r="F326" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="G326" s="9">
@@ -11557,11 +11578,11 @@
         <v>52</v>
       </c>
       <c r="E327" s="6">
-        <f>IF(AND($B327&lt;&gt;"", $G327&lt;&gt;""), ($B327-$G327)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>21.34999999999998</v>
       </c>
       <c r="F327" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G327" s="9">
@@ -11583,11 +11604,11 @@
         <v>54</v>
       </c>
       <c r="E328" s="6">
-        <f>IF(AND($B328&lt;&gt;"", $G328&lt;&gt;""), ($B328-$G328)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>23.366666666666589</v>
       </c>
       <c r="F328" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G328" s="9">
@@ -11609,11 +11630,11 @@
         <v>55</v>
       </c>
       <c r="E329" s="6">
-        <f>IF(AND($B329&lt;&gt;"", $G329&lt;&gt;""), ($B329-$G329)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>25.366666666666582</v>
       </c>
       <c r="F329" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="G329" s="9">
@@ -11635,11 +11656,11 @@
         <v>55</v>
       </c>
       <c r="E330" s="6">
-        <f>IF(AND($B330&lt;&gt;"", $G330&lt;&gt;""), ($B330-$G330)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>27.366666666666575</v>
       </c>
       <c r="F330" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G330" s="9">
@@ -11661,11 +11682,11 @@
         <v>57</v>
       </c>
       <c r="E331" s="6">
-        <f>IF(AND($B331&lt;&gt;"", $G331&lt;&gt;""), ($B331-$G331)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>29.383333333333184</v>
       </c>
       <c r="F331" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G331" s="9">
@@ -11687,11 +11708,11 @@
         <v>57</v>
       </c>
       <c r="E332" s="6">
-        <f>IF(AND($B332&lt;&gt;"", $G332&lt;&gt;""), ($B332-$G332)*1440, "")</f>
+        <f t="shared" si="11"/>
         <v>31.383333333333177</v>
       </c>
       <c r="F332" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G332" s="9">
@@ -11739,11 +11760,11 @@
         <v>33</v>
       </c>
       <c r="E334" s="6">
-        <f t="shared" ref="E334:E348" si="6">IF(AND($B334&lt;&gt;"", $G334&lt;&gt;"TBD"), ($B334-$G334)*1440, "")</f>
+        <f t="shared" ref="E334:E349" si="12">IF(AND($B334&lt;&gt;"", $G334&lt;&gt;"TBD"), ($B334-$G334)*1440, "")</f>
         <v>3.6000000000000831</v>
       </c>
       <c r="F334" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G334" s="9">
@@ -11765,11 +11786,11 @@
         <v>38</v>
       </c>
       <c r="E335" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>5.600000000000076</v>
       </c>
       <c r="F335" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G335" s="9">
@@ -11791,11 +11812,11 @@
         <v>41</v>
       </c>
       <c r="E336" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>7.6166666666666849</v>
       </c>
       <c r="F336" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G336" s="9">
@@ -11817,11 +11838,11 @@
         <v>44</v>
       </c>
       <c r="E337" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>9.6333333333334537</v>
       </c>
       <c r="F337" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G337" s="9">
@@ -11843,11 +11864,11 @@
         <v>45</v>
       </c>
       <c r="E338" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>11.633333333333447</v>
       </c>
       <c r="F338" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G338" s="9">
@@ -11869,11 +11890,11 @@
         <v>47</v>
       </c>
       <c r="E339" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>13.650000000000055</v>
       </c>
       <c r="F339" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G339" s="9">
@@ -11895,11 +11916,11 @@
         <v>49</v>
       </c>
       <c r="E340" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>15.650000000000048</v>
       </c>
       <c r="F340" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="G340" s="9">
@@ -11921,11 +11942,11 @@
         <v>49</v>
       </c>
       <c r="E341" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>17.650000000000041</v>
       </c>
       <c r="F341" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G341" s="9">
@@ -11947,11 +11968,11 @@
         <v>52</v>
       </c>
       <c r="E342" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>19.650000000000034</v>
       </c>
       <c r="F342" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G342" s="9">
@@ -11973,11 +11994,11 @@
         <v>52</v>
       </c>
       <c r="E343" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>21.666666666666803</v>
       </c>
       <c r="F343" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G343" s="9">
@@ -11999,11 +12020,11 @@
         <v>54</v>
       </c>
       <c r="E344" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>23.666666666666796</v>
       </c>
       <c r="F344" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G344" s="9">
@@ -12025,11 +12046,11 @@
         <v>55</v>
       </c>
       <c r="E345" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>25.683333333333405</v>
       </c>
       <c r="F345" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G345" s="9">
@@ -12051,11 +12072,11 @@
         <v>55</v>
       </c>
       <c r="E346" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>27.700000000000014</v>
       </c>
       <c r="F346" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="G346" s="9">
@@ -12077,11 +12098,11 @@
         <v>55</v>
       </c>
       <c r="E347" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>29.700000000000006</v>
       </c>
       <c r="F347" s="2">
-        <f t="shared" ref="F347:F369" si="7">IF(AND(D347&lt;&gt;"",C347&lt;&gt;""),D347-C347,"")</f>
+        <f t="shared" ref="F347:F369" si="13">IF(AND(D347&lt;&gt;"",C347&lt;&gt;""),D347-C347,"")</f>
         <v>1</v>
       </c>
       <c r="G347" s="9">
@@ -12103,11 +12124,11 @@
         <v>57</v>
       </c>
       <c r="E348" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>31.716666666666775</v>
       </c>
       <c r="F348" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="G348" s="9">
@@ -12116,2072 +12137,2088 @@
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E349" s="6" t="str">
-        <f>IF(AND($B349&lt;&gt;"", $G349&lt;&gt;""), ($B349-$G349)*1440, "")</f>
-        <v/>
-      </c>
-      <c r="F349" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+      <c r="A349" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B349" s="9">
+        <v>0.46736111111111112</v>
+      </c>
+      <c r="C349" s="7">
+        <v>32</v>
+      </c>
+      <c r="D349" s="2">
+        <v>35</v>
+      </c>
+      <c r="E349" s="6">
+        <f t="shared" si="12"/>
+        <v>3.9999999999999858</v>
+      </c>
+      <c r="F349" s="2">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="G349" s="9">
+        <f>_xlfn.XLOOKUP(Log!A349, 'Daily Summary'!A:A, 'Daily Summary'!C:C, "TBD")</f>
+        <v>0.46458333333333335</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E350" s="6" t="str">
-        <f>IF(AND($B350&lt;&gt;"", $G350&lt;&gt;""), ($B350-$G350)*1440, "")</f>
+        <f t="shared" ref="E349:E412" si="14">IF(AND($B350&lt;&gt;"", $G350&lt;&gt;""), ($B350-$G350)*1440, "")</f>
         <v/>
       </c>
       <c r="F350" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E351" s="6" t="str">
-        <f>IF(AND($B351&lt;&gt;"", $G351&lt;&gt;""), ($B351-$G351)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F351" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E352" s="6" t="str">
-        <f>IF(AND($B352&lt;&gt;"", $G352&lt;&gt;""), ($B352-$G352)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F352" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E353" s="6" t="str">
-        <f>IF(AND($B353&lt;&gt;"", $G353&lt;&gt;""), ($B353-$G353)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F353" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="354" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E354" s="6" t="str">
-        <f>IF(AND($B354&lt;&gt;"", $G354&lt;&gt;""), ($B354-$G354)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F354" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E355" s="6" t="str">
-        <f>IF(AND($B355&lt;&gt;"", $G355&lt;&gt;""), ($B355-$G355)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F355" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E356" s="6" t="str">
-        <f>IF(AND($B356&lt;&gt;"", $G356&lt;&gt;""), ($B356-$G356)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F356" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E357" s="6" t="str">
-        <f>IF(AND($B357&lt;&gt;"", $G357&lt;&gt;""), ($B357-$G357)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F357" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E358" s="6" t="str">
-        <f>IF(AND($B358&lt;&gt;"", $G358&lt;&gt;""), ($B358-$G358)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F358" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E359" s="6" t="str">
-        <f>IF(AND($B359&lt;&gt;"", $G359&lt;&gt;""), ($B359-$G359)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F359" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E360" s="6" t="str">
-        <f>IF(AND($B360&lt;&gt;"", $G360&lt;&gt;""), ($B360-$G360)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F360" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E361" s="6" t="str">
-        <f>IF(AND($B361&lt;&gt;"", $G361&lt;&gt;""), ($B361-$G361)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F361" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E362" s="6" t="str">
-        <f>IF(AND($B362&lt;&gt;"", $G362&lt;&gt;""), ($B362-$G362)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F362" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E363" s="6" t="str">
-        <f>IF(AND($B363&lt;&gt;"", $G363&lt;&gt;""), ($B363-$G363)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F363" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E364" s="6" t="str">
-        <f>IF(AND($B364&lt;&gt;"", $G364&lt;&gt;""), ($B364-$G364)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F364" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E365" s="6" t="str">
-        <f>IF(AND($B365&lt;&gt;"", $G365&lt;&gt;""), ($B365-$G365)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F365" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E366" s="6" t="str">
-        <f>IF(AND($B366&lt;&gt;"", $G366&lt;&gt;""), ($B366-$G366)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F366" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E367" s="6" t="str">
-        <f>IF(AND($B367&lt;&gt;"", $G367&lt;&gt;""), ($B367-$G367)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F367" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E368" s="6" t="str">
-        <f>IF(AND($B368&lt;&gt;"", $G368&lt;&gt;""), ($B368-$G368)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F368" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E369" s="6" t="str">
-        <f>IF(AND($B369&lt;&gt;"", $G369&lt;&gt;""), ($B369-$G369)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F369" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E370" s="6" t="str">
-        <f>IF(AND($B370&lt;&gt;"", $G370&lt;&gt;""), ($B370-$G370)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E371" s="6" t="str">
-        <f>IF(AND($B371&lt;&gt;"", $G371&lt;&gt;""), ($B371-$G371)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E372" s="6" t="str">
-        <f>IF(AND($B372&lt;&gt;"", $G372&lt;&gt;""), ($B372-$G372)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E373" s="6" t="str">
-        <f>IF(AND($B373&lt;&gt;"", $G373&lt;&gt;""), ($B373-$G373)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E374" s="6" t="str">
-        <f>IF(AND($B374&lt;&gt;"", $G374&lt;&gt;""), ($B374-$G374)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E375" s="6" t="str">
-        <f>IF(AND($B375&lt;&gt;"", $G375&lt;&gt;""), ($B375-$G375)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E376" s="6" t="str">
-        <f>IF(AND($B376&lt;&gt;"", $G376&lt;&gt;""), ($B376-$G376)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E377" s="6" t="str">
-        <f>IF(AND($B377&lt;&gt;"", $G377&lt;&gt;""), ($B377-$G377)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E378" s="6" t="str">
-        <f>IF(AND($B378&lt;&gt;"", $G378&lt;&gt;""), ($B378-$G378)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E379" s="6" t="str">
-        <f>IF(AND($B379&lt;&gt;"", $G379&lt;&gt;""), ($B379-$G379)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E380" s="6" t="str">
-        <f>IF(AND($B380&lt;&gt;"", $G380&lt;&gt;""), ($B380-$G380)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E381" s="6" t="str">
-        <f>IF(AND($B381&lt;&gt;"", $G381&lt;&gt;""), ($B381-$G381)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E382" s="6" t="str">
-        <f>IF(AND($B382&lt;&gt;"", $G382&lt;&gt;""), ($B382-$G382)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E383" s="6" t="str">
-        <f>IF(AND($B383&lt;&gt;"", $G383&lt;&gt;""), ($B383-$G383)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E384" s="6" t="str">
-        <f>IF(AND($B384&lt;&gt;"", $G384&lt;&gt;""), ($B384-$G384)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E385" s="6" t="str">
-        <f>IF(AND($B385&lt;&gt;"", $G385&lt;&gt;""), ($B385-$G385)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E386" s="6" t="str">
-        <f>IF(AND($B386&lt;&gt;"", $G386&lt;&gt;""), ($B386-$G386)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E387" s="6" t="str">
-        <f>IF(AND($B387&lt;&gt;"", $G387&lt;&gt;""), ($B387-$G387)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E388" s="6" t="str">
-        <f>IF(AND($B388&lt;&gt;"", $G388&lt;&gt;""), ($B388-$G388)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E389" s="6" t="str">
-        <f>IF(AND($B389&lt;&gt;"", $G389&lt;&gt;""), ($B389-$G389)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E390" s="6" t="str">
-        <f>IF(AND($B390&lt;&gt;"", $G390&lt;&gt;""), ($B390-$G390)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E391" s="6" t="str">
-        <f>IF(AND($B391&lt;&gt;"", $G391&lt;&gt;""), ($B391-$G391)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E392" s="6" t="str">
-        <f>IF(AND($B392&lt;&gt;"", $G392&lt;&gt;""), ($B392-$G392)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E393" s="6" t="str">
-        <f>IF(AND($B393&lt;&gt;"", $G393&lt;&gt;""), ($B393-$G393)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E394" s="6" t="str">
-        <f>IF(AND($B394&lt;&gt;"", $G394&lt;&gt;""), ($B394-$G394)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E395" s="6" t="str">
-        <f>IF(AND($B395&lt;&gt;"", $G395&lt;&gt;""), ($B395-$G395)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E396" s="6" t="str">
-        <f>IF(AND($B396&lt;&gt;"", $G396&lt;&gt;""), ($B396-$G396)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E397" s="6" t="str">
-        <f>IF(AND($B397&lt;&gt;"", $G397&lt;&gt;""), ($B397-$G397)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E398" s="6" t="str">
-        <f>IF(AND($B398&lt;&gt;"", $G398&lt;&gt;""), ($B398-$G398)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E399" s="6" t="str">
-        <f>IF(AND($B399&lt;&gt;"", $G399&lt;&gt;""), ($B399-$G399)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E400" s="6" t="str">
-        <f>IF(AND($B400&lt;&gt;"", $G400&lt;&gt;""), ($B400-$G400)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E401" s="6" t="str">
-        <f>IF(AND($B401&lt;&gt;"", $G401&lt;&gt;""), ($B401-$G401)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E402" s="6" t="str">
-        <f>IF(AND($B402&lt;&gt;"", $G402&lt;&gt;""), ($B402-$G402)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E403" s="6" t="str">
-        <f>IF(AND($B403&lt;&gt;"", $G403&lt;&gt;""), ($B403-$G403)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E404" s="6" t="str">
-        <f>IF(AND($B404&lt;&gt;"", $G404&lt;&gt;""), ($B404-$G404)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E405" s="6" t="str">
-        <f>IF(AND($B405&lt;&gt;"", $G405&lt;&gt;""), ($B405-$G405)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E406" s="6" t="str">
-        <f>IF(AND($B406&lt;&gt;"", $G406&lt;&gt;""), ($B406-$G406)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E407" s="6" t="str">
-        <f>IF(AND($B407&lt;&gt;"", $G407&lt;&gt;""), ($B407-$G407)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E408" s="6" t="str">
-        <f>IF(AND($B408&lt;&gt;"", $G408&lt;&gt;""), ($B408-$G408)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E409" s="6" t="str">
-        <f>IF(AND($B409&lt;&gt;"", $G409&lt;&gt;""), ($B409-$G409)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E410" s="6" t="str">
-        <f>IF(AND($B410&lt;&gt;"", $G410&lt;&gt;""), ($B410-$G410)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E411" s="6" t="str">
-        <f>IF(AND($B411&lt;&gt;"", $G411&lt;&gt;""), ($B411-$G411)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E412" s="6" t="str">
-        <f>IF(AND($B412&lt;&gt;"", $G412&lt;&gt;""), ($B412-$G412)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E413" s="6" t="str">
-        <f>IF(AND($B413&lt;&gt;"", $G413&lt;&gt;""), ($B413-$G413)*1440, "")</f>
+        <f t="shared" ref="E413:E476" si="15">IF(AND($B413&lt;&gt;"", $G413&lt;&gt;""), ($B413-$G413)*1440, "")</f>
         <v/>
       </c>
     </row>
     <row r="414" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E414" s="6" t="str">
-        <f>IF(AND($B414&lt;&gt;"", $G414&lt;&gt;""), ($B414-$G414)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E415" s="6" t="str">
-        <f>IF(AND($B415&lt;&gt;"", $G415&lt;&gt;""), ($B415-$G415)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E416" s="6" t="str">
-        <f>IF(AND($B416&lt;&gt;"", $G416&lt;&gt;""), ($B416-$G416)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E417" s="6" t="str">
-        <f>IF(AND($B417&lt;&gt;"", $G417&lt;&gt;""), ($B417-$G417)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="418" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E418" s="6" t="str">
-        <f>IF(AND($B418&lt;&gt;"", $G418&lt;&gt;""), ($B418-$G418)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E419" s="6" t="str">
-        <f>IF(AND($B419&lt;&gt;"", $G419&lt;&gt;""), ($B419-$G419)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E420" s="6" t="str">
-        <f>IF(AND($B420&lt;&gt;"", $G420&lt;&gt;""), ($B420-$G420)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E421" s="6" t="str">
-        <f>IF(AND($B421&lt;&gt;"", $G421&lt;&gt;""), ($B421-$G421)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E422" s="6" t="str">
-        <f>IF(AND($B422&lt;&gt;"", $G422&lt;&gt;""), ($B422-$G422)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E423" s="6" t="str">
-        <f>IF(AND($B423&lt;&gt;"", $G423&lt;&gt;""), ($B423-$G423)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E424" s="6" t="str">
-        <f>IF(AND($B424&lt;&gt;"", $G424&lt;&gt;""), ($B424-$G424)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E425" s="6" t="str">
-        <f>IF(AND($B425&lt;&gt;"", $G425&lt;&gt;""), ($B425-$G425)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E426" s="6" t="str">
-        <f>IF(AND($B426&lt;&gt;"", $G426&lt;&gt;""), ($B426-$G426)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E427" s="6" t="str">
-        <f>IF(AND($B427&lt;&gt;"", $G427&lt;&gt;""), ($B427-$G427)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E428" s="6" t="str">
-        <f>IF(AND($B428&lt;&gt;"", $G428&lt;&gt;""), ($B428-$G428)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E429" s="6" t="str">
-        <f>IF(AND($B429&lt;&gt;"", $G429&lt;&gt;""), ($B429-$G429)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E430" s="6" t="str">
-        <f>IF(AND($B430&lt;&gt;"", $G430&lt;&gt;""), ($B430-$G430)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E431" s="6" t="str">
-        <f>IF(AND($B431&lt;&gt;"", $G431&lt;&gt;""), ($B431-$G431)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E432" s="6" t="str">
-        <f>IF(AND($B432&lt;&gt;"", $G432&lt;&gt;""), ($B432-$G432)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E433" s="6" t="str">
-        <f>IF(AND($B433&lt;&gt;"", $G433&lt;&gt;""), ($B433-$G433)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E434" s="6" t="str">
-        <f>IF(AND($B434&lt;&gt;"", $G434&lt;&gt;""), ($B434-$G434)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E435" s="6" t="str">
-        <f>IF(AND($B435&lt;&gt;"", $G435&lt;&gt;""), ($B435-$G435)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E436" s="6" t="str">
-        <f>IF(AND($B436&lt;&gt;"", $G436&lt;&gt;""), ($B436-$G436)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E437" s="6" t="str">
-        <f>IF(AND($B437&lt;&gt;"", $G437&lt;&gt;""), ($B437-$G437)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E438" s="6" t="str">
-        <f>IF(AND($B438&lt;&gt;"", $G438&lt;&gt;""), ($B438-$G438)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E439" s="6" t="str">
-        <f>IF(AND($B439&lt;&gt;"", $G439&lt;&gt;""), ($B439-$G439)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E440" s="6" t="str">
-        <f>IF(AND($B440&lt;&gt;"", $G440&lt;&gt;""), ($B440-$G440)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E441" s="6" t="str">
-        <f>IF(AND($B441&lt;&gt;"", $G441&lt;&gt;""), ($B441-$G441)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E442" s="6" t="str">
-        <f>IF(AND($B442&lt;&gt;"", $G442&lt;&gt;""), ($B442-$G442)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E443" s="6" t="str">
-        <f>IF(AND($B443&lt;&gt;"", $G443&lt;&gt;""), ($B443-$G443)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E444" s="6" t="str">
-        <f>IF(AND($B444&lt;&gt;"", $G444&lt;&gt;""), ($B444-$G444)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E445" s="6" t="str">
-        <f>IF(AND($B445&lt;&gt;"", $G445&lt;&gt;""), ($B445-$G445)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E446" s="6" t="str">
-        <f>IF(AND($B446&lt;&gt;"", $G446&lt;&gt;""), ($B446-$G446)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E447" s="6" t="str">
-        <f>IF(AND($B447&lt;&gt;"", $G447&lt;&gt;""), ($B447-$G447)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E448" s="6" t="str">
-        <f>IF(AND($B448&lt;&gt;"", $G448&lt;&gt;""), ($B448-$G448)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E449" s="6" t="str">
-        <f>IF(AND($B449&lt;&gt;"", $G449&lt;&gt;""), ($B449-$G449)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E450" s="6" t="str">
-        <f>IF(AND($B450&lt;&gt;"", $G450&lt;&gt;""), ($B450-$G450)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E451" s="6" t="str">
-        <f>IF(AND($B451&lt;&gt;"", $G451&lt;&gt;""), ($B451-$G451)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E452" s="6" t="str">
-        <f>IF(AND($B452&lt;&gt;"", $G452&lt;&gt;""), ($B452-$G452)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E453" s="6" t="str">
-        <f>IF(AND($B453&lt;&gt;"", $G453&lt;&gt;""), ($B453-$G453)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E454" s="6" t="str">
-        <f>IF(AND($B454&lt;&gt;"", $G454&lt;&gt;""), ($B454-$G454)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E455" s="6" t="str">
-        <f>IF(AND($B455&lt;&gt;"", $G455&lt;&gt;""), ($B455-$G455)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E456" s="6" t="str">
-        <f>IF(AND($B456&lt;&gt;"", $G456&lt;&gt;""), ($B456-$G456)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E457" s="6" t="str">
-        <f>IF(AND($B457&lt;&gt;"", $G457&lt;&gt;""), ($B457-$G457)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E458" s="6" t="str">
-        <f>IF(AND($B458&lt;&gt;"", $G458&lt;&gt;""), ($B458-$G458)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E459" s="6" t="str">
-        <f>IF(AND($B459&lt;&gt;"", $G459&lt;&gt;""), ($B459-$G459)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E460" s="6" t="str">
-        <f>IF(AND($B460&lt;&gt;"", $G460&lt;&gt;""), ($B460-$G460)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E461" s="6" t="str">
-        <f>IF(AND($B461&lt;&gt;"", $G461&lt;&gt;""), ($B461-$G461)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E462" s="6" t="str">
-        <f>IF(AND($B462&lt;&gt;"", $G462&lt;&gt;""), ($B462-$G462)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E463" s="6" t="str">
-        <f>IF(AND($B463&lt;&gt;"", $G463&lt;&gt;""), ($B463-$G463)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E464" s="6" t="str">
-        <f>IF(AND($B464&lt;&gt;"", $G464&lt;&gt;""), ($B464-$G464)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E465" s="6" t="str">
-        <f>IF(AND($B465&lt;&gt;"", $G465&lt;&gt;""), ($B465-$G465)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E466" s="6" t="str">
-        <f>IF(AND($B466&lt;&gt;"", $G466&lt;&gt;""), ($B466-$G466)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E467" s="6" t="str">
-        <f>IF(AND($B467&lt;&gt;"", $G467&lt;&gt;""), ($B467-$G467)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E468" s="6" t="str">
-        <f>IF(AND($B468&lt;&gt;"", $G468&lt;&gt;""), ($B468-$G468)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E469" s="6" t="str">
-        <f>IF(AND($B469&lt;&gt;"", $G469&lt;&gt;""), ($B469-$G469)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E470" s="6" t="str">
-        <f>IF(AND($B470&lt;&gt;"", $G470&lt;&gt;""), ($B470-$G470)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E471" s="6" t="str">
-        <f>IF(AND($B471&lt;&gt;"", $G471&lt;&gt;""), ($B471-$G471)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E472" s="6" t="str">
-        <f>IF(AND($B472&lt;&gt;"", $G472&lt;&gt;""), ($B472-$G472)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E473" s="6" t="str">
-        <f>IF(AND($B473&lt;&gt;"", $G473&lt;&gt;""), ($B473-$G473)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E474" s="6" t="str">
-        <f>IF(AND($B474&lt;&gt;"", $G474&lt;&gt;""), ($B474-$G474)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E475" s="6" t="str">
-        <f>IF(AND($B475&lt;&gt;"", $G475&lt;&gt;""), ($B475-$G475)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E476" s="6" t="str">
-        <f>IF(AND($B476&lt;&gt;"", $G476&lt;&gt;""), ($B476-$G476)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E477" s="6" t="str">
-        <f>IF(AND($B477&lt;&gt;"", $G477&lt;&gt;""), ($B477-$G477)*1440, "")</f>
+        <f t="shared" ref="E477:E540" si="16">IF(AND($B477&lt;&gt;"", $G477&lt;&gt;""), ($B477-$G477)*1440, "")</f>
         <v/>
       </c>
     </row>
     <row r="478" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E478" s="6" t="str">
-        <f>IF(AND($B478&lt;&gt;"", $G478&lt;&gt;""), ($B478-$G478)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E479" s="6" t="str">
-        <f>IF(AND($B479&lt;&gt;"", $G479&lt;&gt;""), ($B479-$G479)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E480" s="6" t="str">
-        <f>IF(AND($B480&lt;&gt;"", $G480&lt;&gt;""), ($B480-$G480)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E481" s="6" t="str">
-        <f>IF(AND($B481&lt;&gt;"", $G481&lt;&gt;""), ($B481-$G481)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="482" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E482" s="6" t="str">
-        <f>IF(AND($B482&lt;&gt;"", $G482&lt;&gt;""), ($B482-$G482)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E483" s="6" t="str">
-        <f>IF(AND($B483&lt;&gt;"", $G483&lt;&gt;""), ($B483-$G483)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E484" s="6" t="str">
-        <f>IF(AND($B484&lt;&gt;"", $G484&lt;&gt;""), ($B484-$G484)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E485" s="6" t="str">
-        <f>IF(AND($B485&lt;&gt;"", $G485&lt;&gt;""), ($B485-$G485)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E486" s="6" t="str">
-        <f>IF(AND($B486&lt;&gt;"", $G486&lt;&gt;""), ($B486-$G486)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E487" s="6" t="str">
-        <f>IF(AND($B487&lt;&gt;"", $G487&lt;&gt;""), ($B487-$G487)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E488" s="6" t="str">
-        <f>IF(AND($B488&lt;&gt;"", $G488&lt;&gt;""), ($B488-$G488)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E489" s="6" t="str">
-        <f>IF(AND($B489&lt;&gt;"", $G489&lt;&gt;""), ($B489-$G489)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E490" s="6" t="str">
-        <f>IF(AND($B490&lt;&gt;"", $G490&lt;&gt;""), ($B490-$G490)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E491" s="6" t="str">
-        <f>IF(AND($B491&lt;&gt;"", $G491&lt;&gt;""), ($B491-$G491)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E492" s="6" t="str">
-        <f>IF(AND($B492&lt;&gt;"", $G492&lt;&gt;""), ($B492-$G492)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E493" s="6" t="str">
-        <f>IF(AND($B493&lt;&gt;"", $G493&lt;&gt;""), ($B493-$G493)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E494" s="6" t="str">
-        <f>IF(AND($B494&lt;&gt;"", $G494&lt;&gt;""), ($B494-$G494)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E495" s="6" t="str">
-        <f>IF(AND($B495&lt;&gt;"", $G495&lt;&gt;""), ($B495-$G495)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E496" s="6" t="str">
-        <f>IF(AND($B496&lt;&gt;"", $G496&lt;&gt;""), ($B496-$G496)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E497" s="6" t="str">
-        <f>IF(AND($B497&lt;&gt;"", $G497&lt;&gt;""), ($B497-$G497)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E498" s="6" t="str">
-        <f>IF(AND($B498&lt;&gt;"", $G498&lt;&gt;""), ($B498-$G498)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E499" s="6" t="str">
-        <f>IF(AND($B499&lt;&gt;"", $G499&lt;&gt;""), ($B499-$G499)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E500" s="6" t="str">
-        <f>IF(AND($B500&lt;&gt;"", $G500&lt;&gt;""), ($B500-$G500)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E501" s="6" t="str">
-        <f>IF(AND($B501&lt;&gt;"", $G501&lt;&gt;""), ($B501-$G501)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E502" s="6" t="str">
-        <f>IF(AND($B502&lt;&gt;"", $G502&lt;&gt;""), ($B502-$G502)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E503" s="6" t="str">
-        <f>IF(AND($B503&lt;&gt;"", $G503&lt;&gt;""), ($B503-$G503)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E504" s="6" t="str">
-        <f>IF(AND($B504&lt;&gt;"", $G504&lt;&gt;""), ($B504-$G504)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E505" s="6" t="str">
-        <f>IF(AND($B505&lt;&gt;"", $G505&lt;&gt;""), ($B505-$G505)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E506" s="6" t="str">
-        <f>IF(AND($B506&lt;&gt;"", $G506&lt;&gt;""), ($B506-$G506)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E507" s="6" t="str">
-        <f>IF(AND($B507&lt;&gt;"", $G507&lt;&gt;""), ($B507-$G507)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E508" s="6" t="str">
-        <f>IF(AND($B508&lt;&gt;"", $G508&lt;&gt;""), ($B508-$G508)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E509" s="6" t="str">
-        <f>IF(AND($B509&lt;&gt;"", $G509&lt;&gt;""), ($B509-$G509)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E510" s="6" t="str">
-        <f>IF(AND($B510&lt;&gt;"", $G510&lt;&gt;""), ($B510-$G510)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E511" s="6" t="str">
-        <f>IF(AND($B511&lt;&gt;"", $G511&lt;&gt;""), ($B511-$G511)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E512" s="6" t="str">
-        <f>IF(AND($B512&lt;&gt;"", $G512&lt;&gt;""), ($B512-$G512)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E513" s="6" t="str">
-        <f>IF(AND($B513&lt;&gt;"", $G513&lt;&gt;""), ($B513-$G513)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E514" s="6" t="str">
-        <f>IF(AND($B514&lt;&gt;"", $G514&lt;&gt;""), ($B514-$G514)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E515" s="6" t="str">
-        <f>IF(AND($B515&lt;&gt;"", $G515&lt;&gt;""), ($B515-$G515)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E516" s="6" t="str">
-        <f>IF(AND($B516&lt;&gt;"", $G516&lt;&gt;""), ($B516-$G516)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E517" s="6" t="str">
-        <f>IF(AND($B517&lt;&gt;"", $G517&lt;&gt;""), ($B517-$G517)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E518" s="6" t="str">
-        <f>IF(AND($B518&lt;&gt;"", $G518&lt;&gt;""), ($B518-$G518)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E519" s="6" t="str">
-        <f>IF(AND($B519&lt;&gt;"", $G519&lt;&gt;""), ($B519-$G519)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E520" s="6" t="str">
-        <f>IF(AND($B520&lt;&gt;"", $G520&lt;&gt;""), ($B520-$G520)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E521" s="6" t="str">
-        <f>IF(AND($B521&lt;&gt;"", $G521&lt;&gt;""), ($B521-$G521)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E522" s="6" t="str">
-        <f>IF(AND($B522&lt;&gt;"", $G522&lt;&gt;""), ($B522-$G522)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E523" s="6" t="str">
-        <f>IF(AND($B523&lt;&gt;"", $G523&lt;&gt;""), ($B523-$G523)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E524" s="6" t="str">
-        <f>IF(AND($B524&lt;&gt;"", $G524&lt;&gt;""), ($B524-$G524)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E525" s="6" t="str">
-        <f>IF(AND($B525&lt;&gt;"", $G525&lt;&gt;""), ($B525-$G525)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E526" s="6" t="str">
-        <f>IF(AND($B526&lt;&gt;"", $G526&lt;&gt;""), ($B526-$G526)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E527" s="6" t="str">
-        <f>IF(AND($B527&lt;&gt;"", $G527&lt;&gt;""), ($B527-$G527)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E528" s="6" t="str">
-        <f>IF(AND($B528&lt;&gt;"", $G528&lt;&gt;""), ($B528-$G528)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E529" s="6" t="str">
-        <f>IF(AND($B529&lt;&gt;"", $G529&lt;&gt;""), ($B529-$G529)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E530" s="6" t="str">
-        <f>IF(AND($B530&lt;&gt;"", $G530&lt;&gt;""), ($B530-$G530)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E531" s="6" t="str">
-        <f>IF(AND($B531&lt;&gt;"", $G531&lt;&gt;""), ($B531-$G531)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E532" s="6" t="str">
-        <f>IF(AND($B532&lt;&gt;"", $G532&lt;&gt;""), ($B532-$G532)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E533" s="6" t="str">
-        <f>IF(AND($B533&lt;&gt;"", $G533&lt;&gt;""), ($B533-$G533)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E534" s="6" t="str">
-        <f>IF(AND($B534&lt;&gt;"", $G534&lt;&gt;""), ($B534-$G534)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E535" s="6" t="str">
-        <f>IF(AND($B535&lt;&gt;"", $G535&lt;&gt;""), ($B535-$G535)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E536" s="6" t="str">
-        <f>IF(AND($B536&lt;&gt;"", $G536&lt;&gt;""), ($B536-$G536)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E537" s="6" t="str">
-        <f>IF(AND($B537&lt;&gt;"", $G537&lt;&gt;""), ($B537-$G537)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E538" s="6" t="str">
-        <f>IF(AND($B538&lt;&gt;"", $G538&lt;&gt;""), ($B538-$G538)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E539" s="6" t="str">
-        <f>IF(AND($B539&lt;&gt;"", $G539&lt;&gt;""), ($B539-$G539)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E540" s="6" t="str">
-        <f>IF(AND($B540&lt;&gt;"", $G540&lt;&gt;""), ($B540-$G540)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E541" s="6" t="str">
-        <f>IF(AND($B541&lt;&gt;"", $G541&lt;&gt;""), ($B541-$G541)*1440, "")</f>
+        <f t="shared" ref="E541:E604" si="17">IF(AND($B541&lt;&gt;"", $G541&lt;&gt;""), ($B541-$G541)*1440, "")</f>
         <v/>
       </c>
     </row>
     <row r="542" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E542" s="6" t="str">
-        <f>IF(AND($B542&lt;&gt;"", $G542&lt;&gt;""), ($B542-$G542)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E543" s="6" t="str">
-        <f>IF(AND($B543&lt;&gt;"", $G543&lt;&gt;""), ($B543-$G543)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E544" s="6" t="str">
-        <f>IF(AND($B544&lt;&gt;"", $G544&lt;&gt;""), ($B544-$G544)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E545" s="6" t="str">
-        <f>IF(AND($B545&lt;&gt;"", $G545&lt;&gt;""), ($B545-$G545)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="546" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E546" s="6" t="str">
-        <f>IF(AND($B546&lt;&gt;"", $G546&lt;&gt;""), ($B546-$G546)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E547" s="6" t="str">
-        <f>IF(AND($B547&lt;&gt;"", $G547&lt;&gt;""), ($B547-$G547)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E548" s="6" t="str">
-        <f>IF(AND($B548&lt;&gt;"", $G548&lt;&gt;""), ($B548-$G548)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E549" s="6" t="str">
-        <f>IF(AND($B549&lt;&gt;"", $G549&lt;&gt;""), ($B549-$G549)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E550" s="6" t="str">
-        <f>IF(AND($B550&lt;&gt;"", $G550&lt;&gt;""), ($B550-$G550)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E551" s="6" t="str">
-        <f>IF(AND($B551&lt;&gt;"", $G551&lt;&gt;""), ($B551-$G551)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E552" s="6" t="str">
-        <f>IF(AND($B552&lt;&gt;"", $G552&lt;&gt;""), ($B552-$G552)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E553" s="6" t="str">
-        <f>IF(AND($B553&lt;&gt;"", $G553&lt;&gt;""), ($B553-$G553)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E554" s="6" t="str">
-        <f>IF(AND($B554&lt;&gt;"", $G554&lt;&gt;""), ($B554-$G554)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E555" s="6" t="str">
-        <f>IF(AND($B555&lt;&gt;"", $G555&lt;&gt;""), ($B555-$G555)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E556" s="6" t="str">
-        <f>IF(AND($B556&lt;&gt;"", $G556&lt;&gt;""), ($B556-$G556)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E557" s="6" t="str">
-        <f>IF(AND($B557&lt;&gt;"", $G557&lt;&gt;""), ($B557-$G557)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E558" s="6" t="str">
-        <f>IF(AND($B558&lt;&gt;"", $G558&lt;&gt;""), ($B558-$G558)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E559" s="6" t="str">
-        <f>IF(AND($B559&lt;&gt;"", $G559&lt;&gt;""), ($B559-$G559)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E560" s="6" t="str">
-        <f>IF(AND($B560&lt;&gt;"", $G560&lt;&gt;""), ($B560-$G560)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E561" s="6" t="str">
-        <f>IF(AND($B561&lt;&gt;"", $G561&lt;&gt;""), ($B561-$G561)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E562" s="6" t="str">
-        <f>IF(AND($B562&lt;&gt;"", $G562&lt;&gt;""), ($B562-$G562)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E563" s="6" t="str">
-        <f>IF(AND($B563&lt;&gt;"", $G563&lt;&gt;""), ($B563-$G563)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E564" s="6" t="str">
-        <f>IF(AND($B564&lt;&gt;"", $G564&lt;&gt;""), ($B564-$G564)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E565" s="6" t="str">
-        <f>IF(AND($B565&lt;&gt;"", $G565&lt;&gt;""), ($B565-$G565)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E566" s="6" t="str">
-        <f>IF(AND($B566&lt;&gt;"", $G566&lt;&gt;""), ($B566-$G566)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E567" s="6" t="str">
-        <f>IF(AND($B567&lt;&gt;"", $G567&lt;&gt;""), ($B567-$G567)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E568" s="6" t="str">
-        <f>IF(AND($B568&lt;&gt;"", $G568&lt;&gt;""), ($B568-$G568)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E569" s="6" t="str">
-        <f>IF(AND($B569&lt;&gt;"", $G569&lt;&gt;""), ($B569-$G569)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E570" s="6" t="str">
-        <f>IF(AND($B570&lt;&gt;"", $G570&lt;&gt;""), ($B570-$G570)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E571" s="6" t="str">
-        <f>IF(AND($B571&lt;&gt;"", $G571&lt;&gt;""), ($B571-$G571)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E572" s="6" t="str">
-        <f>IF(AND($B572&lt;&gt;"", $G572&lt;&gt;""), ($B572-$G572)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E573" s="6" t="str">
-        <f>IF(AND($B573&lt;&gt;"", $G573&lt;&gt;""), ($B573-$G573)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E574" s="6" t="str">
-        <f>IF(AND($B574&lt;&gt;"", $G574&lt;&gt;""), ($B574-$G574)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E575" s="6" t="str">
-        <f>IF(AND($B575&lt;&gt;"", $G575&lt;&gt;""), ($B575-$G575)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E576" s="6" t="str">
-        <f>IF(AND($B576&lt;&gt;"", $G576&lt;&gt;""), ($B576-$G576)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E577" s="6" t="str">
-        <f>IF(AND($B577&lt;&gt;"", $G577&lt;&gt;""), ($B577-$G577)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E578" s="6" t="str">
-        <f>IF(AND($B578&lt;&gt;"", $G578&lt;&gt;""), ($B578-$G578)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E579" s="6" t="str">
-        <f>IF(AND($B579&lt;&gt;"", $G579&lt;&gt;""), ($B579-$G579)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E580" s="6" t="str">
-        <f>IF(AND($B580&lt;&gt;"", $G580&lt;&gt;""), ($B580-$G580)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E581" s="6" t="str">
-        <f>IF(AND($B581&lt;&gt;"", $G581&lt;&gt;""), ($B581-$G581)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E582" s="6" t="str">
-        <f>IF(AND($B582&lt;&gt;"", $G582&lt;&gt;""), ($B582-$G582)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E583" s="6" t="str">
-        <f>IF(AND($B583&lt;&gt;"", $G583&lt;&gt;""), ($B583-$G583)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E584" s="6" t="str">
-        <f>IF(AND($B584&lt;&gt;"", $G584&lt;&gt;""), ($B584-$G584)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E585" s="6" t="str">
-        <f>IF(AND($B585&lt;&gt;"", $G585&lt;&gt;""), ($B585-$G585)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E586" s="6" t="str">
-        <f>IF(AND($B586&lt;&gt;"", $G586&lt;&gt;""), ($B586-$G586)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E587" s="6" t="str">
-        <f>IF(AND($B587&lt;&gt;"", $G587&lt;&gt;""), ($B587-$G587)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E588" s="6" t="str">
-        <f>IF(AND($B588&lt;&gt;"", $G588&lt;&gt;""), ($B588-$G588)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E589" s="6" t="str">
-        <f>IF(AND($B589&lt;&gt;"", $G589&lt;&gt;""), ($B589-$G589)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E590" s="6" t="str">
-        <f>IF(AND($B590&lt;&gt;"", $G590&lt;&gt;""), ($B590-$G590)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E591" s="6" t="str">
-        <f>IF(AND($B591&lt;&gt;"", $G591&lt;&gt;""), ($B591-$G591)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E592" s="6" t="str">
-        <f>IF(AND($B592&lt;&gt;"", $G592&lt;&gt;""), ($B592-$G592)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E593" s="6" t="str">
-        <f>IF(AND($B593&lt;&gt;"", $G593&lt;&gt;""), ($B593-$G593)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E594" s="6" t="str">
-        <f>IF(AND($B594&lt;&gt;"", $G594&lt;&gt;""), ($B594-$G594)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E595" s="6" t="str">
-        <f>IF(AND($B595&lt;&gt;"", $G595&lt;&gt;""), ($B595-$G595)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E596" s="6" t="str">
-        <f>IF(AND($B596&lt;&gt;"", $G596&lt;&gt;""), ($B596-$G596)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E597" s="6" t="str">
-        <f>IF(AND($B597&lt;&gt;"", $G597&lt;&gt;""), ($B597-$G597)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E598" s="6" t="str">
-        <f>IF(AND($B598&lt;&gt;"", $G598&lt;&gt;""), ($B598-$G598)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E599" s="6" t="str">
-        <f>IF(AND($B599&lt;&gt;"", $G599&lt;&gt;""), ($B599-$G599)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E600" s="6" t="str">
-        <f>IF(AND($B600&lt;&gt;"", $G600&lt;&gt;""), ($B600-$G600)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E601" s="6" t="str">
-        <f>IF(AND($B601&lt;&gt;"", $G601&lt;&gt;""), ($B601-$G601)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E602" s="6" t="str">
-        <f>IF(AND($B602&lt;&gt;"", $G602&lt;&gt;""), ($B602-$G602)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E603" s="6" t="str">
-        <f>IF(AND($B603&lt;&gt;"", $G603&lt;&gt;""), ($B603-$G603)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E604" s="6" t="str">
-        <f>IF(AND($B604&lt;&gt;"", $G604&lt;&gt;""), ($B604-$G604)*1440, "")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E605" s="6" t="str">
-        <f>IF(AND($B605&lt;&gt;"", $G605&lt;&gt;""), ($B605-$G605)*1440, "")</f>
+        <f t="shared" ref="E605:E668" si="18">IF(AND($B605&lt;&gt;"", $G605&lt;&gt;""), ($B605-$G605)*1440, "")</f>
         <v/>
       </c>
     </row>
     <row r="606" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E606" s="6" t="str">
-        <f>IF(AND($B606&lt;&gt;"", $G606&lt;&gt;""), ($B606-$G606)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E607" s="6" t="str">
-        <f>IF(AND($B607&lt;&gt;"", $G607&lt;&gt;""), ($B607-$G607)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E608" s="6" t="str">
-        <f>IF(AND($B608&lt;&gt;"", $G608&lt;&gt;""), ($B608-$G608)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E609" s="6" t="str">
-        <f>IF(AND($B609&lt;&gt;"", $G609&lt;&gt;""), ($B609-$G609)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="610" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E610" s="6" t="str">
-        <f>IF(AND($B610&lt;&gt;"", $G610&lt;&gt;""), ($B610-$G610)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E611" s="6" t="str">
-        <f>IF(AND($B611&lt;&gt;"", $G611&lt;&gt;""), ($B611-$G611)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E612" s="6" t="str">
-        <f>IF(AND($B612&lt;&gt;"", $G612&lt;&gt;""), ($B612-$G612)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E613" s="6" t="str">
-        <f>IF(AND($B613&lt;&gt;"", $G613&lt;&gt;""), ($B613-$G613)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E614" s="6" t="str">
-        <f>IF(AND($B614&lt;&gt;"", $G614&lt;&gt;""), ($B614-$G614)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E615" s="6" t="str">
-        <f>IF(AND($B615&lt;&gt;"", $G615&lt;&gt;""), ($B615-$G615)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E616" s="6" t="str">
-        <f>IF(AND($B616&lt;&gt;"", $G616&lt;&gt;""), ($B616-$G616)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E617" s="6" t="str">
-        <f>IF(AND($B617&lt;&gt;"", $G617&lt;&gt;""), ($B617-$G617)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E618" s="6" t="str">
-        <f>IF(AND($B618&lt;&gt;"", $G618&lt;&gt;""), ($B618-$G618)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E619" s="6" t="str">
-        <f>IF(AND($B619&lt;&gt;"", $G619&lt;&gt;""), ($B619-$G619)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E620" s="6" t="str">
-        <f>IF(AND($B620&lt;&gt;"", $G620&lt;&gt;""), ($B620-$G620)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E621" s="6" t="str">
-        <f>IF(AND($B621&lt;&gt;"", $G621&lt;&gt;""), ($B621-$G621)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E622" s="6" t="str">
-        <f>IF(AND($B622&lt;&gt;"", $G622&lt;&gt;""), ($B622-$G622)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E623" s="6" t="str">
-        <f>IF(AND($B623&lt;&gt;"", $G623&lt;&gt;""), ($B623-$G623)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E624" s="6" t="str">
-        <f>IF(AND($B624&lt;&gt;"", $G624&lt;&gt;""), ($B624-$G624)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E625" s="6" t="str">
-        <f>IF(AND($B625&lt;&gt;"", $G625&lt;&gt;""), ($B625-$G625)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E626" s="6" t="str">
-        <f>IF(AND($B626&lt;&gt;"", $G626&lt;&gt;""), ($B626-$G626)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E627" s="6" t="str">
-        <f>IF(AND($B627&lt;&gt;"", $G627&lt;&gt;""), ($B627-$G627)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E628" s="6" t="str">
-        <f>IF(AND($B628&lt;&gt;"", $G628&lt;&gt;""), ($B628-$G628)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E629" s="6" t="str">
-        <f>IF(AND($B629&lt;&gt;"", $G629&lt;&gt;""), ($B629-$G629)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E630" s="6" t="str">
-        <f>IF(AND($B630&lt;&gt;"", $G630&lt;&gt;""), ($B630-$G630)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E631" s="6" t="str">
-        <f>IF(AND($B631&lt;&gt;"", $G631&lt;&gt;""), ($B631-$G631)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E632" s="6" t="str">
-        <f>IF(AND($B632&lt;&gt;"", $G632&lt;&gt;""), ($B632-$G632)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E633" s="6" t="str">
-        <f>IF(AND($B633&lt;&gt;"", $G633&lt;&gt;""), ($B633-$G633)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E634" s="6" t="str">
-        <f>IF(AND($B634&lt;&gt;"", $G634&lt;&gt;""), ($B634-$G634)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E635" s="6" t="str">
-        <f>IF(AND($B635&lt;&gt;"", $G635&lt;&gt;""), ($B635-$G635)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E636" s="6" t="str">
-        <f>IF(AND($B636&lt;&gt;"", $G636&lt;&gt;""), ($B636-$G636)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E637" s="6" t="str">
-        <f>IF(AND($B637&lt;&gt;"", $G637&lt;&gt;""), ($B637-$G637)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E638" s="6" t="str">
-        <f>IF(AND($B638&lt;&gt;"", $G638&lt;&gt;""), ($B638-$G638)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E639" s="6" t="str">
-        <f>IF(AND($B639&lt;&gt;"", $G639&lt;&gt;""), ($B639-$G639)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E640" s="6" t="str">
-        <f>IF(AND($B640&lt;&gt;"", $G640&lt;&gt;""), ($B640-$G640)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E641" s="6" t="str">
-        <f>IF(AND($B641&lt;&gt;"", $G641&lt;&gt;""), ($B641-$G641)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E642" s="6" t="str">
-        <f>IF(AND($B642&lt;&gt;"", $G642&lt;&gt;""), ($B642-$G642)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E643" s="6" t="str">
-        <f>IF(AND($B643&lt;&gt;"", $G643&lt;&gt;""), ($B643-$G643)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E644" s="6" t="str">
-        <f>IF(AND($B644&lt;&gt;"", $G644&lt;&gt;""), ($B644-$G644)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E645" s="6" t="str">
-        <f>IF(AND($B645&lt;&gt;"", $G645&lt;&gt;""), ($B645-$G645)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E646" s="6" t="str">
-        <f>IF(AND($B646&lt;&gt;"", $G646&lt;&gt;""), ($B646-$G646)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E647" s="6" t="str">
-        <f>IF(AND($B647&lt;&gt;"", $G647&lt;&gt;""), ($B647-$G647)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E648" s="6" t="str">
-        <f>IF(AND($B648&lt;&gt;"", $G648&lt;&gt;""), ($B648-$G648)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E649" s="6" t="str">
-        <f>IF(AND($B649&lt;&gt;"", $G649&lt;&gt;""), ($B649-$G649)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E650" s="6" t="str">
-        <f>IF(AND($B650&lt;&gt;"", $G650&lt;&gt;""), ($B650-$G650)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E651" s="6" t="str">
-        <f>IF(AND($B651&lt;&gt;"", $G651&lt;&gt;""), ($B651-$G651)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E652" s="6" t="str">
-        <f>IF(AND($B652&lt;&gt;"", $G652&lt;&gt;""), ($B652-$G652)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E653" s="6" t="str">
-        <f>IF(AND($B653&lt;&gt;"", $G653&lt;&gt;""), ($B653-$G653)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E654" s="6" t="str">
-        <f>IF(AND($B654&lt;&gt;"", $G654&lt;&gt;""), ($B654-$G654)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E655" s="6" t="str">
-        <f>IF(AND($B655&lt;&gt;"", $G655&lt;&gt;""), ($B655-$G655)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E656" s="6" t="str">
-        <f>IF(AND($B656&lt;&gt;"", $G656&lt;&gt;""), ($B656-$G656)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E657" s="6" t="str">
-        <f>IF(AND($B657&lt;&gt;"", $G657&lt;&gt;""), ($B657-$G657)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E658" s="6" t="str">
-        <f>IF(AND($B658&lt;&gt;"", $G658&lt;&gt;""), ($B658-$G658)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E659" s="6" t="str">
-        <f>IF(AND($B659&lt;&gt;"", $G659&lt;&gt;""), ($B659-$G659)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E660" s="6" t="str">
-        <f>IF(AND($B660&lt;&gt;"", $G660&lt;&gt;""), ($B660-$G660)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E661" s="6" t="str">
-        <f>IF(AND($B661&lt;&gt;"", $G661&lt;&gt;""), ($B661-$G661)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E662" s="6" t="str">
-        <f>IF(AND($B662&lt;&gt;"", $G662&lt;&gt;""), ($B662-$G662)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E663" s="6" t="str">
-        <f>IF(AND($B663&lt;&gt;"", $G663&lt;&gt;""), ($B663-$G663)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E664" s="6" t="str">
-        <f>IF(AND($B664&lt;&gt;"", $G664&lt;&gt;""), ($B664-$G664)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E665" s="6" t="str">
-        <f>IF(AND($B665&lt;&gt;"", $G665&lt;&gt;""), ($B665-$G665)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E666" s="6" t="str">
-        <f>IF(AND($B666&lt;&gt;"", $G666&lt;&gt;""), ($B666-$G666)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E667" s="6" t="str">
-        <f>IF(AND($B667&lt;&gt;"", $G667&lt;&gt;""), ($B667-$G667)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E668" s="6" t="str">
-        <f>IF(AND($B668&lt;&gt;"", $G668&lt;&gt;""), ($B668-$G668)*1440, "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E669" s="6" t="str">
-        <f>IF(AND($B669&lt;&gt;"", $G669&lt;&gt;""), ($B669-$G669)*1440, "")</f>
+        <f t="shared" ref="E669:E679" si="19">IF(AND($B669&lt;&gt;"", $G669&lt;&gt;""), ($B669-$G669)*1440, "")</f>
         <v/>
       </c>
     </row>
     <row r="670" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E670" s="6" t="str">
-        <f>IF(AND($B670&lt;&gt;"", $G670&lt;&gt;""), ($B670-$G670)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E671" s="6" t="str">
-        <f>IF(AND($B671&lt;&gt;"", $G671&lt;&gt;""), ($B671-$G671)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E672" s="6" t="str">
-        <f>IF(AND($B672&lt;&gt;"", $G672&lt;&gt;""), ($B672-$G672)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E673" s="6" t="str">
-        <f>IF(AND($B673&lt;&gt;"", $G673&lt;&gt;""), ($B673-$G673)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="674" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E674" s="6" t="str">
-        <f>IF(AND($B674&lt;&gt;"", $G674&lt;&gt;""), ($B674-$G674)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E675" s="6" t="str">
-        <f>IF(AND($B675&lt;&gt;"", $G675&lt;&gt;""), ($B675-$G675)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E676" s="6" t="str">
-        <f>IF(AND($B676&lt;&gt;"", $G676&lt;&gt;""), ($B676-$G676)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E677" s="6" t="str">
-        <f>IF(AND($B677&lt;&gt;"", $G677&lt;&gt;""), ($B677-$G677)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E678" s="6" t="str">
-        <f>IF(AND($B678&lt;&gt;"", $G678&lt;&gt;""), ($B678-$G678)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E679" s="6" t="str">
-        <f>IF(AND($B679&lt;&gt;"", $G679&lt;&gt;""), ($B679-$G679)*1440, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14190,12 +14227,12 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="C3:D189 E3:XFD3 F4:G204 C190:C204 D191:D204 H1:XFD1 C2:H2 J2:XFD2 H4:XFD25 H26:K33 N26:XFD33 H34:XFD37 I38:XFD38 H39:XFD204 C205:D317 B349:F1048576 H335:XFD1048576 B2:B317 F205:XFD317 E4:E317 B318:XFD333 A1:A1048576 G2:G1048576 F334:XFD334 B334:E348 F335:G348">
+  <conditionalFormatting sqref="A1:A1048576 B2:B317 E3:XFD3 C3:D189 F4:G204 E4:E317 C190:C204 C205:D317 F205:XFD317 B318:XFD333 F334:XFD334 B334:E348 F335:G348 H1:XFD1 C2:H2 J2:XFD2 H4:XFD25 H26:K33 N26:XFD33 H34:XFD37 I38:XFD38 H39:XFD204 D191:D204 H335:XFD1048576 B349:F1048576 G2:G1048576">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:D189 C190:C204 C205:D317 B349:F9993 A3:B317 A318:A9993 E3:G317 G318:G9993 B318:G348">
+  <conditionalFormatting sqref="C3:D189 A3:B317 E3:G317 C190:C204 C205:D317 B318:G348 A318:A9993 B349:F9993 G318:G9993">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>#REF!&lt;&gt;""</formula>
     </cfRule>
@@ -14244,7 +14281,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" cm="1">
-        <f t="array" ref="A2:A28">_xlfn.UNIQUE(Log!$A$3:$A$2486)</f>
+        <f t="array" ref="A2:A29">_xlfn.UNIQUE(Log!$A$3:$A$2486)</f>
         <v>46228</v>
       </c>
       <c r="B2" s="2">
@@ -14665,11 +14702,23 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B28" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.46458333333333335</v>
+      </c>
+      <c r="D28" s="51">
+        <f>IF(C28="", "–", _xlfn.MINIFS(Log!$E$3:$E$1986, Log!$A$3:$A$1986, $A28, Log!$C$3:$C$1986,"&gt;=50"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
+      <c r="A29" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
